--- a/00_Data/Raw/Wind_Series/Maxaranguape.xlsx
+++ b/00_Data/Raw/Wind_Series/Maxaranguape.xlsx
@@ -6,21 +6,18 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t xml:space="preserve">Data</t>
+    <t xml:space="preserve">Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Geração</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vento</t>
+    <t xml:space="preserve">Wind_speed</t>
   </si>
 </sst>
 </file>
@@ -364,18 +361,12 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
         <v>30682</v>
       </c>
       <c r="B2" t="n">
-        <v>0.543790322580645</v>
-      </c>
-      <c r="C2" t="n">
         <v>7.5101626344086</v>
       </c>
     </row>
@@ -384,9 +375,6 @@
         <v>30713</v>
       </c>
       <c r="B3" t="n">
-        <v>0.554591954022989</v>
-      </c>
-      <c r="C3" t="n">
         <v>7.61727729885058</v>
       </c>
     </row>
@@ -395,9 +383,6 @@
         <v>30742</v>
       </c>
       <c r="B4" t="n">
-        <v>0.205430107526882</v>
-      </c>
-      <c r="C4" t="n">
         <v>4.82352150537634</v>
       </c>
     </row>
@@ -406,9 +391,6 @@
         <v>30773</v>
       </c>
       <c r="B5" t="n">
-        <v>0.252808333333333</v>
-      </c>
-      <c r="C5" t="n">
         <v>5.21355</v>
       </c>
     </row>
@@ -417,9 +399,6 @@
         <v>30803</v>
       </c>
       <c r="B6" t="n">
-        <v>0.530604838709677</v>
-      </c>
-      <c r="C6" t="n">
         <v>7.41869758064516</v>
       </c>
     </row>
@@ -428,9 +407,6 @@
         <v>30834</v>
       </c>
       <c r="B7" t="n">
-        <v>0.690419444444444</v>
-      </c>
-      <c r="C7" t="n">
         <v>8.59843888888889</v>
       </c>
     </row>
@@ -439,9 +415,6 @@
         <v>30864</v>
       </c>
       <c r="B8" t="n">
-        <v>0.752245967741936</v>
-      </c>
-      <c r="C8" t="n">
         <v>9.11944489247312</v>
       </c>
     </row>
@@ -450,9 +423,6 @@
         <v>30895</v>
       </c>
       <c r="B9" t="n">
-        <v>0.764185483870968</v>
-      </c>
-      <c r="C9" t="n">
         <v>9.25289919354839</v>
       </c>
     </row>
@@ -461,9 +431,6 @@
         <v>30926</v>
       </c>
       <c r="B10" t="n">
-        <v>0.727877777777778</v>
-      </c>
-      <c r="C10" t="n">
         <v>8.93749861111111</v>
       </c>
     </row>
@@ -472,9 +439,6 @@
         <v>30956</v>
       </c>
       <c r="B11" t="n">
-        <v>0.773395161290323</v>
-      </c>
-      <c r="C11" t="n">
         <v>9.36938037634409</v>
       </c>
     </row>
@@ -483,9 +447,6 @@
         <v>30987</v>
       </c>
       <c r="B12" t="n">
-        <v>0.736986111111111</v>
-      </c>
-      <c r="C12" t="n">
         <v>9.04794444444445</v>
       </c>
     </row>
@@ -494,9 +455,6 @@
         <v>31017</v>
       </c>
       <c r="B13" t="n">
-        <v>0.612024193548387</v>
-      </c>
-      <c r="C13" t="n">
         <v>7.9948252688172</v>
       </c>
     </row>
@@ -505,9 +463,6 @@
         <v>31048</v>
       </c>
       <c r="B14" t="n">
-        <v>0.327795698924731</v>
-      </c>
-      <c r="C14" t="n">
         <v>5.91406048387097</v>
       </c>
     </row>
@@ -516,9 +471,6 @@
         <v>31079</v>
       </c>
       <c r="B15" t="n">
-        <v>0.215330357142857</v>
-      </c>
-      <c r="C15" t="n">
         <v>5.0302693452381</v>
       </c>
     </row>
@@ -527,9 +479,6 @@
         <v>31107</v>
       </c>
       <c r="B16" t="n">
-        <v>0.195231182795699</v>
-      </c>
-      <c r="C16" t="n">
         <v>4.71140188172043</v>
       </c>
     </row>
@@ -538,9 +487,6 @@
         <v>31138</v>
       </c>
       <c r="B17" t="n">
-        <v>0.163145833333333</v>
-      </c>
-      <c r="C17" t="n">
         <v>4.29177083333333</v>
       </c>
     </row>
@@ -549,9 +495,6 @@
         <v>31168</v>
       </c>
       <c r="B18" t="n">
-        <v>0.51695564516129</v>
-      </c>
-      <c r="C18" t="n">
         <v>7.3477997311828</v>
       </c>
     </row>
@@ -560,9 +503,6 @@
         <v>31199</v>
       </c>
       <c r="B19" t="n">
-        <v>0.530301388888889</v>
-      </c>
-      <c r="C19" t="n">
         <v>7.53973888888889</v>
       </c>
     </row>
@@ -571,9 +511,6 @@
         <v>31229</v>
       </c>
       <c r="B20" t="n">
-        <v>0.731397849462366</v>
-      </c>
-      <c r="C20" t="n">
         <v>9.21336827956989</v>
       </c>
     </row>
@@ -582,9 +519,6 @@
         <v>31260</v>
       </c>
       <c r="B21" t="n">
-        <v>0.771466397849462</v>
-      </c>
-      <c r="C21" t="n">
         <v>9.43001747311828</v>
       </c>
     </row>
@@ -593,9 +527,6 @@
         <v>31291</v>
       </c>
       <c r="B22" t="n">
-        <v>0.763556944444444</v>
-      </c>
-      <c r="C22" t="n">
         <v>9.28941666666667</v>
       </c>
     </row>
@@ -604,9 +535,6 @@
         <v>31321</v>
       </c>
       <c r="B23" t="n">
-        <v>0.728831989247312</v>
-      </c>
-      <c r="C23" t="n">
         <v>8.86634811827957</v>
       </c>
     </row>
@@ -615,9 +543,6 @@
         <v>31352</v>
       </c>
       <c r="B24" t="n">
-        <v>0.711749652294854</v>
-      </c>
-      <c r="C24" t="n">
         <v>8.94852712100139</v>
       </c>
     </row>
@@ -626,9 +551,6 @@
         <v>31382</v>
       </c>
       <c r="B25" t="n">
-        <v>0.563729838709677</v>
-      </c>
-      <c r="C25" t="n">
         <v>7.66317876344086</v>
       </c>
     </row>
@@ -637,9 +559,6 @@
         <v>31413</v>
       </c>
       <c r="B26" t="n">
-        <v>0.581849462365591</v>
-      </c>
-      <c r="C26" t="n">
         <v>7.87402284946237</v>
       </c>
     </row>
@@ -648,9 +567,6 @@
         <v>31444</v>
       </c>
       <c r="B27" t="n">
-        <v>0.319849702380952</v>
-      </c>
-      <c r="C27" t="n">
         <v>5.77294791666667</v>
       </c>
     </row>
@@ -659,9 +575,6 @@
         <v>31472</v>
       </c>
       <c r="B28" t="n">
-        <v>0.145740591397849</v>
-      </c>
-      <c r="C28" t="n">
         <v>4.20856048387097</v>
       </c>
     </row>
@@ -670,9 +583,6 @@
         <v>31503</v>
       </c>
       <c r="B29" t="n">
-        <v>0.322647222222222</v>
-      </c>
-      <c r="C29" t="n">
         <v>5.88799166666667</v>
       </c>
     </row>
@@ -681,9 +591,6 @@
         <v>31533</v>
       </c>
       <c r="B30" t="n">
-        <v>0.682774193548387</v>
-      </c>
-      <c r="C30" t="n">
         <v>8.53906451612903</v>
       </c>
     </row>
@@ -692,9 +599,6 @@
         <v>31564</v>
       </c>
       <c r="B31" t="n">
-        <v>0.78245</v>
-      </c>
-      <c r="C31" t="n">
         <v>9.52270555555556</v>
       </c>
     </row>
@@ -703,9 +607,6 @@
         <v>31594</v>
       </c>
       <c r="B32" t="n">
-        <v>0.696173387096774</v>
-      </c>
-      <c r="C32" t="n">
         <v>8.70834274193548</v>
       </c>
     </row>
@@ -714,9 +615,6 @@
         <v>31625</v>
       </c>
       <c r="B33" t="n">
-        <v>0.719665322580645</v>
-      </c>
-      <c r="C33" t="n">
         <v>8.87013978494624</v>
       </c>
     </row>
@@ -725,9 +623,6 @@
         <v>31656</v>
       </c>
       <c r="B34" t="n">
-        <v>0.793006944444444</v>
-      </c>
-      <c r="C34" t="n">
         <v>9.49726527777778</v>
       </c>
     </row>
@@ -736,9 +631,6 @@
         <v>31686</v>
       </c>
       <c r="B35" t="n">
-        <v>0.72563930013459</v>
-      </c>
-      <c r="C35" t="n">
         <v>8.86543876177658</v>
       </c>
     </row>
@@ -747,9 +639,6 @@
         <v>31717</v>
       </c>
       <c r="B36" t="n">
-        <v>0.7782125</v>
-      </c>
-      <c r="C36" t="n">
         <v>9.41732638888889</v>
       </c>
     </row>
@@ -758,9 +647,6 @@
         <v>31747</v>
       </c>
       <c r="B37" t="n">
-        <v>0.668927419354839</v>
-      </c>
-      <c r="C37" t="n">
         <v>8.45225537634409</v>
       </c>
     </row>
@@ -769,9 +655,6 @@
         <v>31778</v>
       </c>
       <c r="B38" t="n">
-        <v>0.601095430107527</v>
-      </c>
-      <c r="C38" t="n">
         <v>7.9094502688172</v>
       </c>
     </row>
@@ -780,9 +663,6 @@
         <v>31809</v>
       </c>
       <c r="B39" t="n">
-        <v>0.572888392857143</v>
-      </c>
-      <c r="C39" t="n">
         <v>7.7658943452381</v>
       </c>
     </row>
@@ -791,9 +671,6 @@
         <v>31837</v>
       </c>
       <c r="B40" t="n">
-        <v>0.256487903225806</v>
-      </c>
-      <c r="C40" t="n">
         <v>5.39556720430108</v>
       </c>
     </row>
@@ -802,9 +679,6 @@
         <v>31868</v>
       </c>
       <c r="B41" t="n">
-        <v>0.587602777777778</v>
-      </c>
-      <c r="C41" t="n">
         <v>7.92514305555556</v>
       </c>
     </row>
@@ -813,9 +687,6 @@
         <v>31898</v>
       </c>
       <c r="B42" t="n">
-        <v>0.660895161290323</v>
-      </c>
-      <c r="C42" t="n">
         <v>8.44970430107527</v>
       </c>
     </row>
@@ -824,9 +695,6 @@
         <v>31929</v>
       </c>
       <c r="B43" t="n">
-        <v>0.685595833333333</v>
-      </c>
-      <c r="C43" t="n">
         <v>8.53450972222222</v>
       </c>
     </row>
@@ -835,9 +703,6 @@
         <v>31959</v>
       </c>
       <c r="B44" t="n">
-        <v>0.777673387096774</v>
-      </c>
-      <c r="C44" t="n">
         <v>9.36181182795699</v>
       </c>
     </row>
@@ -846,9 +711,6 @@
         <v>31990</v>
       </c>
       <c r="B45" t="n">
-        <v>0.769447580645161</v>
-      </c>
-      <c r="C45" t="n">
         <v>9.34758198924731</v>
       </c>
     </row>
@@ -857,9 +719,6 @@
         <v>32021</v>
       </c>
       <c r="B46" t="n">
-        <v>0.789820833333333</v>
-      </c>
-      <c r="C46" t="n">
         <v>9.47189305555556</v>
       </c>
     </row>
@@ -868,9 +727,6 @@
         <v>32051</v>
       </c>
       <c r="B47" t="n">
-        <v>0.714729475100942</v>
-      </c>
-      <c r="C47" t="n">
         <v>8.81635397039031</v>
       </c>
     </row>
@@ -879,9 +735,6 @@
         <v>32082</v>
       </c>
       <c r="B48" t="n">
-        <v>0.7252125</v>
-      </c>
-      <c r="C48" t="n">
         <v>8.890375</v>
       </c>
     </row>
@@ -890,9 +743,6 @@
         <v>32112</v>
       </c>
       <c r="B49" t="n">
-        <v>0.746694892473118</v>
-      </c>
-      <c r="C49" t="n">
         <v>9.05446505376344</v>
       </c>
     </row>
@@ -901,9 +751,6 @@
         <v>32143</v>
       </c>
       <c r="B50" t="n">
-        <v>0.506139784946237</v>
-      </c>
-      <c r="C50" t="n">
         <v>7.26651612903226</v>
       </c>
     </row>
@@ -912,9 +759,6 @@
         <v>32174</v>
       </c>
       <c r="B51" t="n">
-        <v>0.53414224137931</v>
-      </c>
-      <c r="C51" t="n">
         <v>7.45446264367816</v>
       </c>
     </row>
@@ -923,9 +767,6 @@
         <v>32203</v>
       </c>
       <c r="B52" t="n">
-        <v>0.312591397849462</v>
-      </c>
-      <c r="C52" t="n">
         <v>5.74741397849462</v>
       </c>
     </row>
@@ -934,9 +775,6 @@
         <v>32234</v>
       </c>
       <c r="B53" t="n">
-        <v>0.364301388888889</v>
-      </c>
-      <c r="C53" t="n">
         <v>6.19886805555556</v>
       </c>
     </row>
@@ -945,9 +783,6 @@
         <v>32264</v>
       </c>
       <c r="B54" t="n">
-        <v>0.637926075268817</v>
-      </c>
-      <c r="C54" t="n">
         <v>8.18987231182796</v>
       </c>
     </row>
@@ -956,9 +791,6 @@
         <v>32295</v>
       </c>
       <c r="B55" t="n">
-        <v>0.745386111111111</v>
-      </c>
-      <c r="C55" t="n">
         <v>9.22151111111111</v>
       </c>
     </row>
@@ -967,9 +799,6 @@
         <v>32325</v>
       </c>
       <c r="B56" t="n">
-        <v>0.810725806451613</v>
-      </c>
-      <c r="C56" t="n">
         <v>9.90049596774194</v>
       </c>
     </row>
@@ -978,9 +807,6 @@
         <v>32356</v>
       </c>
       <c r="B57" t="n">
-        <v>0.849430107526882</v>
-      </c>
-      <c r="C57" t="n">
         <v>10.3255913978495</v>
       </c>
     </row>
@@ -989,9 +815,6 @@
         <v>32387</v>
       </c>
       <c r="B58" t="n">
-        <v>0.847765277777778</v>
-      </c>
-      <c r="C58" t="n">
         <v>10.2132833333333</v>
       </c>
     </row>
@@ -1000,9 +823,6 @@
         <v>32417</v>
       </c>
       <c r="B59" t="n">
-        <v>0.764102288021534</v>
-      </c>
-      <c r="C59" t="n">
         <v>9.22205248990579</v>
       </c>
     </row>
@@ -1011,9 +831,6 @@
         <v>32448</v>
       </c>
       <c r="B60" t="n">
-        <v>0.736927777777778</v>
-      </c>
-      <c r="C60" t="n">
         <v>9.011725</v>
       </c>
     </row>
@@ -1022,9 +839,6 @@
         <v>32478</v>
       </c>
       <c r="B61" t="n">
-        <v>0.565275537634409</v>
-      </c>
-      <c r="C61" t="n">
         <v>7.70877150537634</v>
       </c>
     </row>
@@ -1033,9 +847,6 @@
         <v>32509</v>
       </c>
       <c r="B62" t="n">
-        <v>0.556130376344086</v>
-      </c>
-      <c r="C62" t="n">
         <v>7.61017607526882</v>
       </c>
     </row>
@@ -1044,9 +855,6 @@
         <v>32540</v>
       </c>
       <c r="B63" t="n">
-        <v>0.562474702380952</v>
-      </c>
-      <c r="C63" t="n">
         <v>7.663125</v>
       </c>
     </row>
@@ -1055,9 +863,6 @@
         <v>32568</v>
       </c>
       <c r="B64" t="n">
-        <v>0.334674731182796</v>
-      </c>
-      <c r="C64" t="n">
         <v>5.9539623655914</v>
       </c>
     </row>
@@ -1066,9 +871,6 @@
         <v>32599</v>
       </c>
       <c r="B65" t="n">
-        <v>0.199026388888889</v>
-      </c>
-      <c r="C65" t="n">
         <v>4.82806111111111</v>
       </c>
     </row>
@@ -1077,9 +879,6 @@
         <v>32629</v>
       </c>
       <c r="B66" t="n">
-        <v>0.458120967741936</v>
-      </c>
-      <c r="C66" t="n">
         <v>6.87475</v>
       </c>
     </row>
@@ -1088,9 +887,6 @@
         <v>32660</v>
       </c>
       <c r="B67" t="n">
-        <v>0.579752777777778</v>
-      </c>
-      <c r="C67" t="n">
         <v>7.81961111111111</v>
       </c>
     </row>
@@ -1099,9 +895,6 @@
         <v>32690</v>
       </c>
       <c r="B68" t="n">
-        <v>0.628702956989247</v>
-      </c>
-      <c r="C68" t="n">
         <v>8.27102822580645</v>
       </c>
     </row>
@@ -1110,9 +903,6 @@
         <v>32721</v>
       </c>
       <c r="B69" t="n">
-        <v>0.789033602150538</v>
-      </c>
-      <c r="C69" t="n">
         <v>9.49765053763441</v>
       </c>
     </row>
@@ -1121,9 +911,6 @@
         <v>32752</v>
       </c>
       <c r="B70" t="n">
-        <v>0.715351388888889</v>
-      </c>
-      <c r="C70" t="n">
         <v>8.91041805555555</v>
       </c>
     </row>
@@ -1132,9 +919,6 @@
         <v>32782</v>
       </c>
       <c r="B71" t="n">
-        <v>0.766652759084791</v>
-      </c>
-      <c r="C71" t="n">
         <v>9.36114401076716</v>
       </c>
     </row>
@@ -1143,9 +927,6 @@
         <v>32813</v>
       </c>
       <c r="B72" t="n">
-        <v>0.696731944444444</v>
-      </c>
-      <c r="C72" t="n">
         <v>8.69668888888889</v>
       </c>
     </row>
@@ -1154,9 +935,6 @@
         <v>32843</v>
       </c>
       <c r="B73" t="n">
-        <v>0.633100806451613</v>
-      </c>
-      <c r="C73" t="n">
         <v>8.19208333333333</v>
       </c>
     </row>
@@ -1165,9 +943,6 @@
         <v>32874</v>
       </c>
       <c r="B74" t="n">
-        <v>0.745728494623656</v>
-      </c>
-      <c r="C74" t="n">
         <v>9.08534811827957</v>
       </c>
     </row>
@@ -1176,9 +951,6 @@
         <v>32905</v>
       </c>
       <c r="B75" t="n">
-        <v>0.478861607142857</v>
-      </c>
-      <c r="C75" t="n">
         <v>7.16203125</v>
       </c>
     </row>
@@ -1187,9 +959,6 @@
         <v>32933</v>
       </c>
       <c r="B76" t="n">
-        <v>0.648943548387097</v>
-      </c>
-      <c r="C76" t="n">
         <v>8.28771774193548</v>
       </c>
     </row>
@@ -1198,9 +967,6 @@
         <v>32964</v>
       </c>
       <c r="B77" t="n">
-        <v>0.6318875</v>
-      </c>
-      <c r="C77" t="n">
         <v>8.16436111111111</v>
       </c>
     </row>
@@ -1209,9 +975,6 @@
         <v>32994</v>
       </c>
       <c r="B78" t="n">
-        <v>0.593520161290323</v>
-      </c>
-      <c r="C78" t="n">
         <v>7.91527956989247</v>
       </c>
     </row>
@@ -1220,9 +983,6 @@
         <v>33025</v>
       </c>
       <c r="B79" t="n">
-        <v>0.776077777777778</v>
-      </c>
-      <c r="C79" t="n">
         <v>9.35146388888889</v>
       </c>
     </row>
@@ -1231,9 +991,6 @@
         <v>33055</v>
       </c>
       <c r="B80" t="n">
-        <v>0.671653225806452</v>
-      </c>
-      <c r="C80" t="n">
         <v>8.51767204301075</v>
       </c>
     </row>
@@ -1242,9 +999,6 @@
         <v>33086</v>
       </c>
       <c r="B81" t="n">
-        <v>0.807235215053763</v>
-      </c>
-      <c r="C81" t="n">
         <v>9.65483602150538</v>
       </c>
     </row>
@@ -1253,9 +1007,6 @@
         <v>33117</v>
       </c>
       <c r="B82" t="n">
-        <v>0.766504166666667</v>
-      </c>
-      <c r="C82" t="n">
         <v>9.28899166666667</v>
       </c>
     </row>
@@ -1264,9 +1015,6 @@
         <v>33147</v>
       </c>
       <c r="B83" t="n">
-        <v>0.786736204576043</v>
-      </c>
-      <c r="C83" t="n">
         <v>9.50456393001346</v>
       </c>
     </row>
@@ -1275,9 +1023,6 @@
         <v>33178</v>
       </c>
       <c r="B84" t="n">
-        <v>0.728934722222222</v>
-      </c>
-      <c r="C84" t="n">
         <v>8.95421805555556</v>
       </c>
     </row>
@@ -1286,9 +1031,6 @@
         <v>33208</v>
       </c>
       <c r="B85" t="n">
-        <v>0.671823924731183</v>
-      </c>
-      <c r="C85" t="n">
         <v>8.43943817204301</v>
       </c>
     </row>
@@ -1297,9 +1039,6 @@
         <v>33239</v>
       </c>
       <c r="B86" t="n">
-        <v>0.603760752688172</v>
-      </c>
-      <c r="C86" t="n">
         <v>7.95245833333333</v>
       </c>
     </row>
@@ -1308,9 +1047,6 @@
         <v>33270</v>
       </c>
       <c r="B87" t="n">
-        <v>0.524840773809524</v>
-      </c>
-      <c r="C87" t="n">
         <v>7.40684523809524</v>
       </c>
     </row>
@@ -1319,9 +1055,6 @@
         <v>33298</v>
       </c>
       <c r="B88" t="n">
-        <v>0.503971774193548</v>
-      </c>
-      <c r="C88" t="n">
         <v>7.21585483870968</v>
       </c>
     </row>
@@ -1330,9 +1063,6 @@
         <v>33329</v>
       </c>
       <c r="B89" t="n">
-        <v>0.461968055555556</v>
-      </c>
-      <c r="C89" t="n">
         <v>6.91045277777778</v>
       </c>
     </row>
@@ -1341,9 +1071,6 @@
         <v>33359</v>
       </c>
       <c r="B90" t="n">
-        <v>0.605875</v>
-      </c>
-      <c r="C90" t="n">
         <v>8.0736747311828</v>
       </c>
     </row>
@@ -1352,9 +1079,6 @@
         <v>33390</v>
       </c>
       <c r="B91" t="n">
-        <v>0.791870833333333</v>
-      </c>
-      <c r="C91" t="n">
         <v>9.52065277777778</v>
       </c>
     </row>
@@ -1363,9 +1087,6 @@
         <v>33420</v>
       </c>
       <c r="B92" t="n">
-        <v>0.847852150537634</v>
-      </c>
-      <c r="C92" t="n">
         <v>10.3460981182796</v>
       </c>
     </row>
@@ -1374,9 +1095,6 @@
         <v>33451</v>
       </c>
       <c r="B93" t="n">
-        <v>0.867329301075269</v>
-      </c>
-      <c r="C93" t="n">
         <v>10.5884556451613</v>
       </c>
     </row>
@@ -1385,9 +1103,6 @@
         <v>33482</v>
       </c>
       <c r="B94" t="n">
-        <v>0.8069875</v>
-      </c>
-      <c r="C94" t="n">
         <v>9.78510138888889</v>
       </c>
     </row>
@@ -1396,9 +1111,6 @@
         <v>33512</v>
       </c>
       <c r="B95" t="n">
-        <v>0.810422611036339</v>
-      </c>
-      <c r="C95" t="n">
         <v>9.76904306864065</v>
       </c>
     </row>
@@ -1407,9 +1119,6 @@
         <v>33543</v>
       </c>
       <c r="B96" t="n">
-        <v>0.697923611111111</v>
-      </c>
-      <c r="C96" t="n">
         <v>8.69435138888889</v>
       </c>
     </row>
@@ -1418,9 +1127,6 @@
         <v>33573</v>
       </c>
       <c r="B97" t="n">
-        <v>0.647735215053763</v>
-      </c>
-      <c r="C97" t="n">
         <v>8.27971370967742</v>
       </c>
     </row>
@@ -1429,9 +1135,6 @@
         <v>33604</v>
       </c>
       <c r="B98" t="n">
-        <v>0.520068548387097</v>
-      </c>
-      <c r="C98" t="n">
         <v>7.41434274193548</v>
       </c>
     </row>
@@ -1440,9 +1143,6 @@
         <v>33635</v>
       </c>
       <c r="B99" t="n">
-        <v>0.612146551724138</v>
-      </c>
-      <c r="C99" t="n">
         <v>7.99398132183908</v>
       </c>
     </row>
@@ -1451,9 +1151,6 @@
         <v>33664</v>
       </c>
       <c r="B100" t="n">
-        <v>0.630322580645161</v>
-      </c>
-      <c r="C100" t="n">
         <v>8.22780779569892</v>
       </c>
     </row>
@@ -1462,9 +1159,6 @@
         <v>33695</v>
       </c>
       <c r="B101" t="n">
-        <v>0.626159722222222</v>
-      </c>
-      <c r="C101" t="n">
         <v>8.21374861111111</v>
       </c>
     </row>
@@ -1473,9 +1167,6 @@
         <v>33725</v>
       </c>
       <c r="B102" t="n">
-        <v>0.654689516129032</v>
-      </c>
-      <c r="C102" t="n">
         <v>8.3331626344086</v>
       </c>
     </row>
@@ -1484,9 +1175,6 @@
         <v>33756</v>
       </c>
       <c r="B103" t="n">
-        <v>0.744793055555556</v>
-      </c>
-      <c r="C103" t="n">
         <v>9.04774861111111</v>
       </c>
     </row>
@@ -1495,9 +1183,6 @@
         <v>33786</v>
       </c>
       <c r="B104" t="n">
-        <v>0.777028225806452</v>
-      </c>
-      <c r="C104" t="n">
         <v>9.38117607526882</v>
       </c>
     </row>
@@ -1506,9 +1191,6 @@
         <v>33817</v>
       </c>
       <c r="B105" t="n">
-        <v>0.811084677419355</v>
-      </c>
-      <c r="C105" t="n">
         <v>9.75901344086022</v>
       </c>
     </row>
@@ -1517,9 +1199,6 @@
         <v>33848</v>
       </c>
       <c r="B106" t="n">
-        <v>0.835861111111111</v>
-      </c>
-      <c r="C106" t="n">
         <v>10.0014319444444</v>
       </c>
     </row>
@@ -1528,9 +1207,6 @@
         <v>33878</v>
       </c>
       <c r="B107" t="n">
-        <v>0.808095558546433</v>
-      </c>
-      <c r="C107" t="n">
         <v>9.69145895020188</v>
       </c>
     </row>
@@ -1539,9 +1215,6 @@
         <v>33909</v>
       </c>
       <c r="B108" t="n">
-        <v>0.74905</v>
-      </c>
-      <c r="C108" t="n">
         <v>9.09214861111111</v>
       </c>
     </row>
@@ -1550,9 +1223,6 @@
         <v>33939</v>
       </c>
       <c r="B109" t="n">
-        <v>0.700298387096774</v>
-      </c>
-      <c r="C109" t="n">
         <v>8.79409408602151</v>
       </c>
     </row>
@@ -1561,9 +1231,6 @@
         <v>33970</v>
       </c>
       <c r="B110" t="n">
-        <v>0.661702956989247</v>
-      </c>
-      <c r="C110" t="n">
         <v>8.526375</v>
       </c>
     </row>
@@ -1572,9 +1239,6 @@
         <v>34001</v>
       </c>
       <c r="B111" t="n">
-        <v>0.649171130952381</v>
-      </c>
-      <c r="C111" t="n">
         <v>8.28441071428571</v>
       </c>
     </row>
@@ -1583,9 +1247,6 @@
         <v>34029</v>
       </c>
       <c r="B112" t="n">
-        <v>0.644801075268817</v>
-      </c>
-      <c r="C112" t="n">
         <v>8.25554032258064</v>
       </c>
     </row>
@@ -1594,9 +1255,6 @@
         <v>34060</v>
       </c>
       <c r="B113" t="n">
-        <v>0.653625</v>
-      </c>
-      <c r="C113" t="n">
         <v>8.31744444444444</v>
       </c>
     </row>
@@ -1605,9 +1263,6 @@
         <v>34090</v>
       </c>
       <c r="B114" t="n">
-        <v>0.718801075268817</v>
-      </c>
-      <c r="C114" t="n">
         <v>8.92473655913978</v>
       </c>
     </row>
@@ -1616,9 +1271,6 @@
         <v>34121</v>
       </c>
       <c r="B115" t="n">
-        <v>0.788018055555556</v>
-      </c>
-      <c r="C115" t="n">
         <v>9.50011111111111</v>
       </c>
     </row>
@@ -1627,9 +1279,6 @@
         <v>34151</v>
       </c>
       <c r="B116" t="n">
-        <v>0.781305107526882</v>
-      </c>
-      <c r="C116" t="n">
         <v>9.48392876344086</v>
       </c>
     </row>
@@ -1638,9 +1287,6 @@
         <v>34182</v>
       </c>
       <c r="B117" t="n">
-        <v>0.790862903225806</v>
-      </c>
-      <c r="C117" t="n">
         <v>9.53345295698925</v>
       </c>
     </row>
@@ -1649,9 +1295,6 @@
         <v>34213</v>
       </c>
       <c r="B118" t="n">
-        <v>0.729359722222222</v>
-      </c>
-      <c r="C118" t="n">
         <v>9.00825138888889</v>
       </c>
     </row>
@@ -1660,9 +1303,6 @@
         <v>34243</v>
       </c>
       <c r="B119" t="n">
-        <v>0.761561238223419</v>
-      </c>
-      <c r="C119" t="n">
         <v>9.45456393001346</v>
       </c>
     </row>
@@ -1671,9 +1311,6 @@
         <v>34274</v>
       </c>
       <c r="B120" t="n">
-        <v>0.765618055555556</v>
-      </c>
-      <c r="C120" t="n">
         <v>9.40542638888889</v>
       </c>
     </row>
@@ -1682,9 +1319,6 @@
         <v>34304</v>
       </c>
       <c r="B121" t="n">
-        <v>0.715680107526882</v>
-      </c>
-      <c r="C121" t="n">
         <v>8.83594758064516</v>
       </c>
     </row>
@@ -1693,9 +1327,6 @@
         <v>34335</v>
       </c>
       <c r="B122" t="n">
-        <v>0.491745967741935</v>
-      </c>
-      <c r="C122" t="n">
         <v>7.15390860215054</v>
       </c>
     </row>
@@ -1704,9 +1335,6 @@
         <v>34366</v>
       </c>
       <c r="B123" t="n">
-        <v>0.55200744047619</v>
-      </c>
-      <c r="C123" t="n">
         <v>7.58779910714286</v>
       </c>
     </row>
@@ -1715,9 +1343,6 @@
         <v>34394</v>
       </c>
       <c r="B124" t="n">
-        <v>0.40002688172043</v>
-      </c>
-      <c r="C124" t="n">
         <v>6.49939919354839</v>
       </c>
     </row>
@@ -1726,9 +1351,6 @@
         <v>34425</v>
       </c>
       <c r="B125" t="n">
-        <v>0.470156944444444</v>
-      </c>
-      <c r="C125" t="n">
         <v>6.97267638888889</v>
       </c>
     </row>
@@ -1737,9 +1359,6 @@
         <v>34455</v>
       </c>
       <c r="B126" t="n">
-        <v>0.627493279569892</v>
-      </c>
-      <c r="C126" t="n">
         <v>8.15063306451613</v>
       </c>
     </row>
@@ -1748,9 +1367,6 @@
         <v>34486</v>
       </c>
       <c r="B127" t="n">
-        <v>0.553325</v>
-      </c>
-      <c r="C127" t="n">
         <v>7.59051527777778</v>
       </c>
     </row>
@@ -1759,9 +1375,6 @@
         <v>34516</v>
       </c>
       <c r="B128" t="n">
-        <v>0.790131720430107</v>
-      </c>
-      <c r="C128" t="n">
         <v>9.49686155913978</v>
       </c>
     </row>
@@ -1770,9 +1383,6 @@
         <v>34547</v>
       </c>
       <c r="B129" t="n">
-        <v>0.810086021505376</v>
-      </c>
-      <c r="C129" t="n">
         <v>9.78680376344086</v>
       </c>
     </row>
@@ -1781,9 +1391,6 @@
         <v>34578</v>
       </c>
       <c r="B130" t="n">
-        <v>0.843533333333333</v>
-      </c>
-      <c r="C130" t="n">
         <v>10.1281875</v>
       </c>
     </row>
@@ -1792,9 +1399,6 @@
         <v>34608</v>
       </c>
       <c r="B131" t="n">
-        <v>0.805551816958277</v>
-      </c>
-      <c r="C131" t="n">
         <v>9.82791520861373</v>
       </c>
     </row>
@@ -1803,9 +1407,6 @@
         <v>34639</v>
       </c>
       <c r="B132" t="n">
-        <v>0.774736111111111</v>
-      </c>
-      <c r="C132" t="n">
         <v>9.34190833333333</v>
       </c>
     </row>
@@ -1814,9 +1415,6 @@
         <v>34669</v>
       </c>
       <c r="B133" t="n">
-        <v>0.704206989247312</v>
-      </c>
-      <c r="C133" t="n">
         <v>8.83147983870968</v>
       </c>
     </row>
@@ -1825,9 +1423,6 @@
         <v>34700</v>
       </c>
       <c r="B134" t="n">
-        <v>0.586286290322581</v>
-      </c>
-      <c r="C134" t="n">
         <v>7.82040591397849</v>
       </c>
     </row>
@@ -1836,9 +1431,6 @@
         <v>34731</v>
       </c>
       <c r="B135" t="n">
-        <v>0.382703869047619</v>
-      </c>
-      <c r="C135" t="n">
         <v>6.36186755952381</v>
       </c>
     </row>
@@ -1847,9 +1439,6 @@
         <v>34759</v>
       </c>
       <c r="B136" t="n">
-        <v>0.464772849462366</v>
-      </c>
-      <c r="C136" t="n">
         <v>6.94811155913979</v>
       </c>
     </row>
@@ -1858,9 +1447,6 @@
         <v>34790</v>
       </c>
       <c r="B137" t="n">
-        <v>0.420338888888889</v>
-      </c>
-      <c r="C137" t="n">
         <v>6.61294027777778</v>
       </c>
     </row>
@@ -1869,9 +1455,6 @@
         <v>34820</v>
       </c>
       <c r="B138" t="n">
-        <v>0.457731182795699</v>
-      </c>
-      <c r="C138" t="n">
         <v>6.89719489247312</v>
       </c>
     </row>
@@ -1880,9 +1463,6 @@
         <v>34851</v>
       </c>
       <c r="B139" t="n">
-        <v>0.733843055555556</v>
-      </c>
-      <c r="C139" t="n">
         <v>9.05889583333333</v>
       </c>
     </row>
@@ -1891,9 +1471,6 @@
         <v>34881</v>
       </c>
       <c r="B140" t="n">
-        <v>0.817864247311828</v>
-      </c>
-      <c r="C140" t="n">
         <v>9.92478091397849</v>
       </c>
     </row>
@@ -1902,9 +1479,6 @@
         <v>34912</v>
       </c>
       <c r="B141" t="n">
-        <v>0.85479435483871</v>
-      </c>
-      <c r="C141" t="n">
         <v>10.2614758064516</v>
       </c>
     </row>
@@ -1913,9 +1487,6 @@
         <v>34943</v>
       </c>
       <c r="B142" t="n">
-        <v>0.875858333333333</v>
-      </c>
-      <c r="C142" t="n">
         <v>10.6300138888889</v>
       </c>
     </row>
@@ -1924,9 +1495,6 @@
         <v>34973</v>
       </c>
       <c r="B143" t="n">
-        <v>0.754537012113055</v>
-      </c>
-      <c r="C143" t="n">
         <v>9.29356931359354</v>
       </c>
     </row>
@@ -1935,9 +1503,6 @@
         <v>35004</v>
       </c>
       <c r="B144" t="n">
-        <v>0.723245833333333</v>
-      </c>
-      <c r="C144" t="n">
         <v>8.99959722222222</v>
       </c>
     </row>
@@ -1946,9 +1511,6 @@
         <v>35034</v>
       </c>
       <c r="B145" t="n">
-        <v>0.614610215053763</v>
-      </c>
-      <c r="C145" t="n">
         <v>8.03337634408602</v>
       </c>
     </row>
@@ -1957,9 +1519,6 @@
         <v>35065</v>
       </c>
       <c r="B146" t="n">
-        <v>0.648411290322581</v>
-      </c>
-      <c r="C146" t="n">
         <v>8.27720564516129</v>
       </c>
     </row>
@@ -1968,9 +1527,6 @@
         <v>35096</v>
       </c>
       <c r="B147" t="n">
-        <v>0.561278735632184</v>
-      </c>
-      <c r="C147" t="n">
         <v>7.63690229885057</v>
       </c>
     </row>
@@ -1979,9 +1535,6 @@
         <v>35125</v>
       </c>
       <c r="B148" t="n">
-        <v>0.324243279569892</v>
-      </c>
-      <c r="C148" t="n">
         <v>5.85163172043011</v>
       </c>
     </row>
@@ -1990,9 +1543,6 @@
         <v>35156</v>
       </c>
       <c r="B149" t="n">
-        <v>0.263565277777778</v>
-      </c>
-      <c r="C149" t="n">
         <v>5.21917777777778</v>
       </c>
     </row>
@@ -2001,9 +1551,6 @@
         <v>35186</v>
       </c>
       <c r="B150" t="n">
-        <v>0.534056451612903</v>
-      </c>
-      <c r="C150" t="n">
         <v>7.4574502688172</v>
       </c>
     </row>
@@ -2012,9 +1559,6 @@
         <v>35217</v>
       </c>
       <c r="B151" t="n">
-        <v>0.769688888888889</v>
-      </c>
-      <c r="C151" t="n">
         <v>9.43535833333333</v>
       </c>
     </row>
@@ -2023,9 +1567,6 @@
         <v>35247</v>
       </c>
       <c r="B152" t="n">
-        <v>0.815368279569892</v>
-      </c>
-      <c r="C152" t="n">
         <v>9.92732123655914</v>
       </c>
     </row>
@@ -2034,9 +1575,6 @@
         <v>35278</v>
       </c>
       <c r="B153" t="n">
-        <v>0.799452956989247</v>
-      </c>
-      <c r="C153" t="n">
         <v>9.71314650537634</v>
       </c>
     </row>
@@ -2045,9 +1583,6 @@
         <v>35309</v>
       </c>
       <c r="B154" t="n">
-        <v>0.844847222222222</v>
-      </c>
-      <c r="C154" t="n">
         <v>10.2406041666667</v>
       </c>
     </row>
@@ -2056,9 +1591,6 @@
         <v>35339</v>
       </c>
       <c r="B155" t="n">
-        <v>0.791878869448183</v>
-      </c>
-      <c r="C155" t="n">
         <v>9.52330955585464</v>
       </c>
     </row>
@@ -2067,9 +1599,6 @@
         <v>35370</v>
       </c>
       <c r="B156" t="n">
-        <v>0.691066666666667</v>
-      </c>
-      <c r="C156" t="n">
         <v>8.68306666666667</v>
       </c>
     </row>
@@ -2078,9 +1607,6 @@
         <v>35400</v>
       </c>
       <c r="B157" t="n">
-        <v>0.67230376344086</v>
-      </c>
-      <c r="C157" t="n">
         <v>8.46541129032258</v>
       </c>
     </row>
@@ -2089,9 +1615,6 @@
         <v>35431</v>
       </c>
       <c r="B158" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="C158" t="n">
         <v>8.25093279569892</v>
       </c>
     </row>
@@ -2100,9 +1623,6 @@
         <v>35462</v>
       </c>
       <c r="B159" t="n">
-        <v>0.759138392857143</v>
-      </c>
-      <c r="C159" t="n">
         <v>9.17386160714286</v>
       </c>
     </row>
@@ -2111,9 +1631,6 @@
         <v>35490</v>
       </c>
       <c r="B160" t="n">
-        <v>0.51523252688172</v>
-      </c>
-      <c r="C160" t="n">
         <v>7.3858938172043</v>
       </c>
     </row>
@@ -2122,9 +1639,6 @@
         <v>35521</v>
       </c>
       <c r="B161" t="n">
-        <v>0.501126388888889</v>
-      </c>
-      <c r="C161" t="n">
         <v>7.21065277777778</v>
       </c>
     </row>
@@ -2133,9 +1647,6 @@
         <v>35551</v>
       </c>
       <c r="B162" t="n">
-        <v>0.681118279569892</v>
-      </c>
-      <c r="C162" t="n">
         <v>8.64408064516129</v>
       </c>
     </row>
@@ -2144,9 +1655,6 @@
         <v>35582</v>
       </c>
       <c r="B163" t="n">
-        <v>0.681623611111111</v>
-      </c>
-      <c r="C163" t="n">
         <v>8.52067361111111</v>
       </c>
     </row>
@@ -2155,9 +1663,6 @@
         <v>35612</v>
       </c>
       <c r="B164" t="n">
-        <v>0.812579301075269</v>
-      </c>
-      <c r="C164" t="n">
         <v>9.78713978494624</v>
       </c>
     </row>
@@ -2166,9 +1671,6 @@
         <v>35643</v>
       </c>
       <c r="B165" t="n">
-        <v>0.853189516129032</v>
-      </c>
-      <c r="C165" t="n">
         <v>10.3468400537634</v>
       </c>
     </row>
@@ -2177,9 +1679,6 @@
         <v>35674</v>
       </c>
       <c r="B166" t="n">
-        <v>0.692143055555556</v>
-      </c>
-      <c r="C166" t="n">
         <v>8.67939027777778</v>
       </c>
     </row>
@@ -2188,9 +1687,6 @@
         <v>35704</v>
       </c>
       <c r="B167" t="n">
-        <v>0.686372812920592</v>
-      </c>
-      <c r="C167" t="n">
         <v>8.66022072678331</v>
       </c>
     </row>
@@ -2199,9 +1695,6 @@
         <v>35735</v>
       </c>
       <c r="B168" t="n">
-        <v>0.679994444444444</v>
-      </c>
-      <c r="C168" t="n">
         <v>8.57893333333333</v>
       </c>
     </row>
@@ -2210,9 +1703,6 @@
         <v>35765</v>
       </c>
       <c r="B169" t="n">
-        <v>0.556817204301075</v>
-      </c>
-      <c r="C169" t="n">
         <v>7.60052822580645</v>
       </c>
     </row>
@@ -2221,9 +1711,6 @@
         <v>35796</v>
       </c>
       <c r="B170" t="n">
-        <v>0.483352150537634</v>
-      </c>
-      <c r="C170" t="n">
         <v>7.08906720430108</v>
       </c>
     </row>
@@ -2232,9 +1719,6 @@
         <v>35827</v>
       </c>
       <c r="B171" t="n">
-        <v>0.656087797619048</v>
-      </c>
-      <c r="C171" t="n">
         <v>8.3234375</v>
       </c>
     </row>
@@ -2243,9 +1727,6 @@
         <v>35855</v>
       </c>
       <c r="B172" t="n">
-        <v>0.578373655913978</v>
-      </c>
-      <c r="C172" t="n">
         <v>7.81702688172043</v>
       </c>
     </row>
@@ -2254,9 +1735,6 @@
         <v>35886</v>
       </c>
       <c r="B173" t="n">
-        <v>0.724769444444444</v>
-      </c>
-      <c r="C173" t="n">
         <v>8.89380555555556</v>
       </c>
     </row>
@@ -2265,9 +1743,6 @@
         <v>35916</v>
       </c>
       <c r="B174" t="n">
-        <v>0.733008064516129</v>
-      </c>
-      <c r="C174" t="n">
         <v>9.05016666666667</v>
       </c>
     </row>
@@ -2276,9 +1751,6 @@
         <v>35947</v>
       </c>
       <c r="B175" t="n">
-        <v>0.806059722222222</v>
-      </c>
-      <c r="C175" t="n">
         <v>9.7255625</v>
       </c>
     </row>
@@ -2287,9 +1759,6 @@
         <v>35977</v>
       </c>
       <c r="B176" t="n">
-        <v>0.78486559139785</v>
-      </c>
-      <c r="C176" t="n">
         <v>9.51234811827957</v>
       </c>
     </row>
@@ -2298,9 +1767,6 @@
         <v>36008</v>
       </c>
       <c r="B177" t="n">
-        <v>0.830013440860215</v>
-      </c>
-      <c r="C177" t="n">
         <v>9.94926478494624</v>
       </c>
     </row>
@@ -2309,9 +1775,6 @@
         <v>36039</v>
       </c>
       <c r="B178" t="n">
-        <v>0.839322222222222</v>
-      </c>
-      <c r="C178" t="n">
         <v>10.1061694444444</v>
       </c>
     </row>
@@ -2320,9 +1783,6 @@
         <v>36069</v>
       </c>
       <c r="B179" t="n">
-        <v>0.829224764468371</v>
-      </c>
-      <c r="C179" t="n">
         <v>9.97680349932705</v>
       </c>
     </row>
@@ -2331,9 +1791,6 @@
         <v>36100</v>
       </c>
       <c r="B180" t="n">
-        <v>0.680022222222222</v>
-      </c>
-      <c r="C180" t="n">
         <v>8.53615416666667</v>
       </c>
     </row>
@@ -2342,9 +1799,6 @@
         <v>36130</v>
       </c>
       <c r="B181" t="n">
-        <v>0.736090053763441</v>
-      </c>
-      <c r="C181" t="n">
         <v>8.97879301075269</v>
       </c>
     </row>
@@ -2353,9 +1807,6 @@
         <v>36161</v>
       </c>
       <c r="B182" t="n">
-        <v>0.629625</v>
-      </c>
-      <c r="C182" t="n">
         <v>8.14622446236559</v>
       </c>
     </row>
@@ -2364,9 +1815,6 @@
         <v>36192</v>
       </c>
       <c r="B183" t="n">
-        <v>0.696247023809524</v>
-      </c>
-      <c r="C183" t="n">
         <v>8.66975595238095</v>
       </c>
     </row>
@@ -2375,9 +1823,6 @@
         <v>36220</v>
       </c>
       <c r="B184" t="n">
-        <v>0.54994623655914</v>
-      </c>
-      <c r="C184" t="n">
         <v>7.54296639784946</v>
       </c>
     </row>
@@ -2386,9 +1831,6 @@
         <v>36251</v>
       </c>
       <c r="B185" t="n">
-        <v>0.640226388888889</v>
-      </c>
-      <c r="C185" t="n">
         <v>8.20288888888889</v>
       </c>
     </row>
@@ -2397,9 +1839,6 @@
         <v>36281</v>
       </c>
       <c r="B186" t="n">
-        <v>0.576059139784946</v>
-      </c>
-      <c r="C186" t="n">
         <v>7.83911693548387</v>
       </c>
     </row>
@@ -2408,9 +1847,6 @@
         <v>36312</v>
       </c>
       <c r="B187" t="n">
-        <v>0.743797222222222</v>
-      </c>
-      <c r="C187" t="n">
         <v>9.10420833333333</v>
       </c>
     </row>
@@ -2419,9 +1855,6 @@
         <v>36342</v>
       </c>
       <c r="B188" t="n">
-        <v>0.854745967741935</v>
-      </c>
-      <c r="C188" t="n">
         <v>10.4459892473118</v>
       </c>
     </row>
@@ -2430,9 +1863,6 @@
         <v>36373</v>
       </c>
       <c r="B189" t="n">
-        <v>0.883092741935484</v>
-      </c>
-      <c r="C189" t="n">
         <v>10.7814825268817</v>
       </c>
     </row>
@@ -2441,9 +1871,6 @@
         <v>36404</v>
       </c>
       <c r="B190" t="n">
-        <v>0.847280555555556</v>
-      </c>
-      <c r="C190" t="n">
         <v>10.309</v>
       </c>
     </row>
@@ -2452,9 +1879,6 @@
         <v>36434</v>
       </c>
       <c r="B191" t="n">
-        <v>0.754837146702557</v>
-      </c>
-      <c r="C191" t="n">
         <v>9.33738761776582</v>
       </c>
     </row>
@@ -2463,9 +1887,6 @@
         <v>36465</v>
       </c>
       <c r="B192" t="n">
-        <v>0.684461111111111</v>
-      </c>
-      <c r="C192" t="n">
         <v>8.56600277777778</v>
       </c>
     </row>
@@ -2474,9 +1895,6 @@
         <v>36495</v>
       </c>
       <c r="B193" t="n">
-        <v>0.699532258064516</v>
-      </c>
-      <c r="C193" t="n">
         <v>8.77638172043011</v>
       </c>
     </row>
@@ -2485,9 +1903,6 @@
         <v>36526</v>
       </c>
       <c r="B194" t="n">
-        <v>0.552725806451613</v>
-      </c>
-      <c r="C194" t="n">
         <v>7.58534677419355</v>
       </c>
     </row>
@@ -2496,9 +1911,6 @@
         <v>36557</v>
       </c>
       <c r="B195" t="n">
-        <v>0.399162356321839</v>
-      </c>
-      <c r="C195" t="n">
         <v>6.27769252873563</v>
       </c>
     </row>
@@ -2507,9 +1919,6 @@
         <v>36586</v>
       </c>
       <c r="B196" t="n">
-        <v>0.623465053763441</v>
-      </c>
-      <c r="C196" t="n">
         <v>8.07847311827957</v>
       </c>
     </row>
@@ -2518,9 +1927,6 @@
         <v>36617</v>
       </c>
       <c r="B197" t="n">
-        <v>0.547618055555556</v>
-      </c>
-      <c r="C197" t="n">
         <v>7.49555833333333</v>
       </c>
     </row>
@@ -2529,9 +1935,6 @@
         <v>36647</v>
       </c>
       <c r="B198" t="n">
-        <v>0.695475806451613</v>
-      </c>
-      <c r="C198" t="n">
         <v>8.67064784946237</v>
       </c>
     </row>
@@ -2540,9 +1943,6 @@
         <v>36678</v>
       </c>
       <c r="B199" t="n">
-        <v>0.673204166666667</v>
-      </c>
-      <c r="C199" t="n">
         <v>8.55929722222222</v>
       </c>
     </row>
@@ -2551,9 +1951,6 @@
         <v>36708</v>
       </c>
       <c r="B200" t="n">
-        <v>0.738126344086022</v>
-      </c>
-      <c r="C200" t="n">
         <v>9.15351612903226</v>
       </c>
     </row>
@@ -2562,9 +1959,6 @@
         <v>36739</v>
       </c>
       <c r="B201" t="n">
-        <v>0.774970430107527</v>
-      </c>
-      <c r="C201" t="n">
         <v>9.55774865591398</v>
       </c>
     </row>
@@ -2573,9 +1967,6 @@
         <v>36770</v>
       </c>
       <c r="B202" t="n">
-        <v>0.801219444444444</v>
-      </c>
-      <c r="C202" t="n">
         <v>9.69360277777778</v>
       </c>
     </row>
@@ -2584,9 +1975,6 @@
         <v>36800</v>
       </c>
       <c r="B203" t="n">
-        <v>0.810240915208614</v>
-      </c>
-      <c r="C203" t="n">
         <v>9.83896096904441</v>
       </c>
     </row>
@@ -2595,9 +1983,6 @@
         <v>36831</v>
       </c>
       <c r="B204" t="n">
-        <v>0.696747222222222</v>
-      </c>
-      <c r="C204" t="n">
         <v>8.73207083333333</v>
       </c>
     </row>
@@ -2606,9 +1991,6 @@
         <v>36861</v>
       </c>
       <c r="B205" t="n">
-        <v>0.597377688172043</v>
-      </c>
-      <c r="C205" t="n">
         <v>7.87459139784946</v>
       </c>
     </row>
@@ -2617,9 +1999,6 @@
         <v>36892</v>
       </c>
       <c r="B206" t="n">
-        <v>0.706603494623656</v>
-      </c>
-      <c r="C206" t="n">
         <v>8.80442204301075</v>
       </c>
     </row>
@@ -2628,9 +2007,6 @@
         <v>36923</v>
       </c>
       <c r="B207" t="n">
-        <v>0.570348214285714</v>
-      </c>
-      <c r="C207" t="n">
         <v>7.72617410714286</v>
       </c>
     </row>
@@ -2639,9 +2015,6 @@
         <v>36951</v>
       </c>
       <c r="B208" t="n">
-        <v>0.480856182795699</v>
-      </c>
-      <c r="C208" t="n">
         <v>7.10921774193548</v>
       </c>
     </row>
@@ -2650,9 +2023,6 @@
         <v>36982</v>
       </c>
       <c r="B209" t="n">
-        <v>0.574548611111111</v>
-      </c>
-      <c r="C209" t="n">
         <v>7.79043055555556</v>
       </c>
     </row>
@@ -2661,9 +2031,6 @@
         <v>37012</v>
       </c>
       <c r="B210" t="n">
-        <v>0.595120967741935</v>
-      </c>
-      <c r="C210" t="n">
         <v>7.9095685483871</v>
       </c>
     </row>
@@ -2672,9 +2039,6 @@
         <v>37043</v>
       </c>
       <c r="B211" t="n">
-        <v>0.735570833333333</v>
-      </c>
-      <c r="C211" t="n">
         <v>9.08120555555556</v>
       </c>
     </row>
@@ -2683,9 +2047,6 @@
         <v>37073</v>
       </c>
       <c r="B212" t="n">
-        <v>0.790048387096774</v>
-      </c>
-      <c r="C212" t="n">
         <v>9.57111021505376</v>
       </c>
     </row>
@@ -2694,9 +2055,6 @@
         <v>37104</v>
       </c>
       <c r="B213" t="n">
-        <v>0.885916666666667</v>
-      </c>
-      <c r="C213" t="n">
         <v>10.8162809139785</v>
       </c>
     </row>
@@ -2705,9 +2063,6 @@
         <v>37135</v>
       </c>
       <c r="B214" t="n">
-        <v>0.796765277777778</v>
-      </c>
-      <c r="C214" t="n">
         <v>9.71378472222222</v>
       </c>
     </row>
@@ -2716,9 +2071,6 @@
         <v>37165</v>
       </c>
       <c r="B215" t="n">
-        <v>0.708473755047106</v>
-      </c>
-      <c r="C215" t="n">
         <v>8.78351144010767</v>
       </c>
     </row>
@@ -2727,9 +2079,6 @@
         <v>37196</v>
       </c>
       <c r="B216" t="n">
-        <v>0.708120833333333</v>
-      </c>
-      <c r="C216" t="n">
         <v>8.69963194444444</v>
       </c>
     </row>
@@ -2738,9 +2087,6 @@
         <v>37226</v>
       </c>
       <c r="B217" t="n">
-        <v>0.776400537634409</v>
-      </c>
-      <c r="C217" t="n">
         <v>9.37188709677419</v>
       </c>
     </row>
@@ -2749,9 +2095,6 @@
         <v>37257</v>
       </c>
       <c r="B218" t="n">
-        <v>0.511418010752688</v>
-      </c>
-      <c r="C218" t="n">
         <v>7.29418682795699</v>
       </c>
     </row>
@@ -2760,9 +2103,6 @@
         <v>37288</v>
       </c>
       <c r="B219" t="n">
-        <v>0.606592261904762</v>
-      </c>
-      <c r="C219" t="n">
         <v>8.01516517857143</v>
       </c>
     </row>
@@ -2771,9 +2111,6 @@
         <v>37316</v>
       </c>
       <c r="B220" t="n">
-        <v>0.53602688172043</v>
-      </c>
-      <c r="C220" t="n">
         <v>7.46604569892473</v>
       </c>
     </row>
@@ -2782,9 +2119,6 @@
         <v>37347</v>
       </c>
       <c r="B221" t="n">
-        <v>0.576452777777778</v>
-      </c>
-      <c r="C221" t="n">
         <v>7.73781527777778</v>
       </c>
     </row>
@@ -2793,9 +2127,6 @@
         <v>37377</v>
       </c>
       <c r="B222" t="n">
-        <v>0.650654569892473</v>
-      </c>
-      <c r="C222" t="n">
         <v>8.33275537634409</v>
       </c>
     </row>
@@ -2804,9 +2135,6 @@
         <v>37408</v>
       </c>
       <c r="B223" t="n">
-        <v>0.718491666666667</v>
-      </c>
-      <c r="C223" t="n">
         <v>8.90373194444444</v>
       </c>
     </row>
@@ -2815,9 +2143,6 @@
         <v>37438</v>
       </c>
       <c r="B224" t="n">
-        <v>0.719310483870968</v>
-      </c>
-      <c r="C224" t="n">
         <v>8.96888172043011</v>
       </c>
     </row>
@@ -2826,9 +2151,6 @@
         <v>37469</v>
       </c>
       <c r="B225" t="n">
-        <v>0.850865591397849</v>
-      </c>
-      <c r="C225" t="n">
         <v>10.4211559139785</v>
       </c>
     </row>
@@ -2837,9 +2159,6 @@
         <v>37500</v>
       </c>
       <c r="B226" t="n">
-        <v>0.785758333333333</v>
-      </c>
-      <c r="C226" t="n">
         <v>9.58563472222222</v>
       </c>
     </row>
@@ -2848,9 +2167,6 @@
         <v>37530</v>
       </c>
       <c r="B227" t="n">
-        <v>0.842822580645161</v>
-      </c>
-      <c r="C227" t="n">
         <v>10.1823413978495</v>
       </c>
     </row>
@@ -2859,9 +2175,6 @@
         <v>37561</v>
       </c>
       <c r="B228" t="n">
-        <v>0.742666203059805</v>
-      </c>
-      <c r="C228" t="n">
         <v>9.0860083449235</v>
       </c>
     </row>
@@ -2870,9 +2183,6 @@
         <v>37591</v>
       </c>
       <c r="B229" t="n">
-        <v>0.637220430107527</v>
-      </c>
-      <c r="C229" t="n">
         <v>8.2638938172043</v>
       </c>
     </row>
@@ -2881,9 +2191,6 @@
         <v>37622</v>
       </c>
       <c r="B230" t="n">
-        <v>0.403987903225806</v>
-      </c>
-      <c r="C230" t="n">
         <v>6.50540322580645</v>
       </c>
     </row>
@@ -2892,9 +2199,6 @@
         <v>37653</v>
       </c>
       <c r="B231" t="n">
-        <v>0.559840773809524</v>
-      </c>
-      <c r="C231" t="n">
         <v>7.69736458333333</v>
       </c>
     </row>
@@ -2903,9 +2207,6 @@
         <v>37681</v>
       </c>
       <c r="B232" t="n">
-        <v>0.442908602150538</v>
-      </c>
-      <c r="C232" t="n">
         <v>6.79063172043011</v>
       </c>
     </row>
@@ -2914,9 +2215,6 @@
         <v>37712</v>
       </c>
       <c r="B233" t="n">
-        <v>0.511825</v>
-      </c>
-      <c r="C233" t="n">
         <v>7.27879444444444</v>
       </c>
     </row>
@@ -2925,9 +2223,6 @@
         <v>37742</v>
       </c>
       <c r="B234" t="n">
-        <v>0.603608870967742</v>
-      </c>
-      <c r="C234" t="n">
         <v>8.00039784946236</v>
       </c>
     </row>
@@ -2936,9 +2231,6 @@
         <v>37773</v>
       </c>
       <c r="B235" t="n">
-        <v>0.702559722222222</v>
-      </c>
-      <c r="C235" t="n">
         <v>8.74565277777778</v>
       </c>
     </row>
@@ -2947,9 +2239,6 @@
         <v>37803</v>
       </c>
       <c r="B236" t="n">
-        <v>0.817158602150538</v>
-      </c>
-      <c r="C236" t="n">
         <v>10.0190188172043</v>
       </c>
     </row>
@@ -2958,9 +2247,6 @@
         <v>37834</v>
       </c>
       <c r="B237" t="n">
-        <v>0.786004032258064</v>
-      </c>
-      <c r="C237" t="n">
         <v>9.54624193548387</v>
       </c>
     </row>
@@ -2969,9 +2255,6 @@
         <v>37865</v>
       </c>
       <c r="B238" t="n">
-        <v>0.848272222222222</v>
-      </c>
-      <c r="C238" t="n">
         <v>10.3056083333333</v>
       </c>
     </row>
@@ -2980,9 +2263,6 @@
         <v>37895</v>
       </c>
       <c r="B239" t="n">
-        <v>0.828103633916555</v>
-      </c>
-      <c r="C239" t="n">
         <v>10.0038775235532</v>
       </c>
     </row>
@@ -2991,9 +2271,6 @@
         <v>37926</v>
       </c>
       <c r="B240" t="n">
-        <v>0.738851388888889</v>
-      </c>
-      <c r="C240" t="n">
         <v>9.09665972222222</v>
       </c>
     </row>
@@ -3002,9 +2279,6 @@
         <v>37956</v>
       </c>
       <c r="B241" t="n">
-        <v>0.707354838709677</v>
-      </c>
-      <c r="C241" t="n">
         <v>8.77873252688172</v>
       </c>
     </row>
@@ -3013,9 +2287,6 @@
         <v>37987</v>
       </c>
       <c r="B242" t="n">
-        <v>0.421448924731183</v>
-      </c>
-      <c r="C242" t="n">
         <v>6.58511962365591</v>
       </c>
     </row>
@@ -3024,9 +2295,6 @@
         <v>38018</v>
       </c>
       <c r="B243" t="n">
-        <v>0.556712643678161</v>
-      </c>
-      <c r="C243" t="n">
         <v>7.60732471264368</v>
       </c>
     </row>
@@ -3035,9 +2303,6 @@
         <v>38047</v>
       </c>
       <c r="B244" t="n">
-        <v>0.643004032258064</v>
-      </c>
-      <c r="C244" t="n">
         <v>8.31620698924731</v>
       </c>
     </row>
@@ -3046,9 +2311,6 @@
         <v>38078</v>
       </c>
       <c r="B245" t="n">
-        <v>0.641859722222222</v>
-      </c>
-      <c r="C245" t="n">
         <v>8.2338125</v>
       </c>
     </row>
@@ -3057,9 +2319,6 @@
         <v>38108</v>
       </c>
       <c r="B246" t="n">
-        <v>0.61654435483871</v>
-      </c>
-      <c r="C246" t="n">
         <v>8.10238978494624</v>
       </c>
     </row>
@@ -3068,9 +2327,6 @@
         <v>38139</v>
       </c>
       <c r="B247" t="n">
-        <v>0.682356944444444</v>
-      </c>
-      <c r="C247" t="n">
         <v>8.63397361111111</v>
       </c>
     </row>
@@ -3079,9 +2335,6 @@
         <v>38169</v>
       </c>
       <c r="B248" t="n">
-        <v>0.731057795698925</v>
-      </c>
-      <c r="C248" t="n">
         <v>9.04103360215054</v>
       </c>
     </row>
@@ -3090,9 +2343,6 @@
         <v>38200</v>
       </c>
       <c r="B249" t="n">
-        <v>0.812879032258065</v>
-      </c>
-      <c r="C249" t="n">
         <v>9.88724193548387</v>
       </c>
     </row>
@@ -3101,9 +2351,6 @@
         <v>38231</v>
       </c>
       <c r="B250" t="n">
-        <v>0.880334722222222</v>
-      </c>
-      <c r="C250" t="n">
         <v>10.7057291666667</v>
       </c>
     </row>
@@ -3112,9 +2359,6 @@
         <v>38261</v>
       </c>
       <c r="B251" t="n">
-        <v>0.811841397849462</v>
-      </c>
-      <c r="C251" t="n">
         <v>9.79027822580645</v>
       </c>
     </row>
@@ -3123,9 +2367,6 @@
         <v>38292</v>
       </c>
       <c r="B252" t="n">
-        <v>0.772936022253129</v>
-      </c>
-      <c r="C252" t="n">
         <v>9.43986230876217</v>
       </c>
     </row>
@@ -3134,9 +2375,6 @@
         <v>38322</v>
       </c>
       <c r="B253" t="n">
-        <v>0.704903225806452</v>
-      </c>
-      <c r="C253" t="n">
         <v>8.73161962365591</v>
       </c>
     </row>
@@ -3145,9 +2383,6 @@
         <v>38353</v>
       </c>
       <c r="B254" t="n">
-        <v>0.571572580645161</v>
-      </c>
-      <c r="C254" t="n">
         <v>7.7801438172043</v>
       </c>
     </row>
@@ -3156,9 +2391,6 @@
         <v>38384</v>
       </c>
       <c r="B255" t="n">
-        <v>0.600933035714286</v>
-      </c>
-      <c r="C255" t="n">
         <v>8.01508333333333</v>
       </c>
     </row>
@@ -3167,9 +2399,6 @@
         <v>38412</v>
       </c>
       <c r="B256" t="n">
-        <v>0.472352150537634</v>
-      </c>
-      <c r="C256" t="n">
         <v>6.946</v>
       </c>
     </row>
@@ -3178,9 +2407,6 @@
         <v>38443</v>
       </c>
       <c r="B257" t="n">
-        <v>0.676905555555556</v>
-      </c>
-      <c r="C257" t="n">
         <v>8.57960555555556</v>
       </c>
     </row>
@@ -3189,9 +2415,6 @@
         <v>38473</v>
       </c>
       <c r="B258" t="n">
-        <v>0.655201612903226</v>
-      </c>
-      <c r="C258" t="n">
         <v>8.43555376344086</v>
       </c>
     </row>
@@ -3200,9 +2423,6 @@
         <v>38504</v>
       </c>
       <c r="B259" t="n">
-        <v>0.6711125</v>
-      </c>
-      <c r="C259" t="n">
         <v>8.56970555555556</v>
       </c>
     </row>
@@ -3211,9 +2431,6 @@
         <v>38534</v>
       </c>
       <c r="B260" t="n">
-        <v>0.77447311827957</v>
-      </c>
-      <c r="C260" t="n">
         <v>9.57942204301075</v>
       </c>
     </row>
@@ -3222,9 +2439,6 @@
         <v>38565</v>
       </c>
       <c r="B261" t="n">
-        <v>0.836760752688172</v>
-      </c>
-      <c r="C261" t="n">
         <v>10.0801465053763</v>
       </c>
     </row>
@@ -3233,9 +2447,6 @@
         <v>38596</v>
       </c>
       <c r="B262" t="n">
-        <v>0.798161111111111</v>
-      </c>
-      <c r="C262" t="n">
         <v>9.78841666666667</v>
       </c>
     </row>
@@ -3244,9 +2455,6 @@
         <v>38626</v>
       </c>
       <c r="B263" t="n">
-        <v>0.82064333781965</v>
-      </c>
-      <c r="C263" t="n">
         <v>10.0324804845222</v>
       </c>
     </row>
@@ -3255,9 +2463,6 @@
         <v>38657</v>
       </c>
       <c r="B264" t="n">
-        <v>0.777830555555556</v>
-      </c>
-      <c r="C264" t="n">
         <v>9.46476666666667</v>
       </c>
     </row>
@@ -3266,9 +2471,6 @@
         <v>38687</v>
       </c>
       <c r="B265" t="n">
-        <v>0.72632123655914</v>
-      </c>
-      <c r="C265" t="n">
         <v>9.02599865591398</v>
       </c>
     </row>
@@ -3277,9 +2479,6 @@
         <v>38718</v>
       </c>
       <c r="B266" t="n">
-        <v>0.791958333333333</v>
-      </c>
-      <c r="C266" t="n">
         <v>9.53607795698925</v>
       </c>
     </row>
@@ -3288,9 +2487,6 @@
         <v>38749</v>
       </c>
       <c r="B267" t="n">
-        <v>0.420191964285714</v>
-      </c>
-      <c r="C267" t="n">
         <v>6.66130654761905</v>
       </c>
     </row>
@@ -3299,9 +2495,6 @@
         <v>38777</v>
       </c>
       <c r="B268" t="n">
-        <v>0.456905913978495</v>
-      </c>
-      <c r="C268" t="n">
         <v>6.91973252688172</v>
       </c>
     </row>
@@ -3310,9 +2503,6 @@
         <v>38808</v>
       </c>
       <c r="B269" t="n">
-        <v>0.338547222222222</v>
-      </c>
-      <c r="C269" t="n">
         <v>5.98180694444444</v>
       </c>
     </row>
@@ -3321,9 +2511,6 @@
         <v>38838</v>
       </c>
       <c r="B270" t="n">
-        <v>0.57484811827957</v>
-      </c>
-      <c r="C270" t="n">
         <v>7.82629435483871</v>
       </c>
     </row>
@@ -3332,9 +2519,6 @@
         <v>38869</v>
       </c>
       <c r="B271" t="n">
-        <v>0.757805555555556</v>
-      </c>
-      <c r="C271" t="n">
         <v>9.48977222222222</v>
       </c>
     </row>
@@ -3343,9 +2527,6 @@
         <v>38899</v>
       </c>
       <c r="B272" t="n">
-        <v>0.775342741935484</v>
-      </c>
-      <c r="C272" t="n">
         <v>9.62514247311828</v>
       </c>
     </row>
@@ -3354,9 +2535,6 @@
         <v>38930</v>
       </c>
       <c r="B273" t="n">
-        <v>0.813682795698925</v>
-      </c>
-      <c r="C273" t="n">
         <v>9.96324327956989</v>
       </c>
     </row>
@@ -3365,9 +2543,6 @@
         <v>38961</v>
       </c>
       <c r="B274" t="n">
-        <v>0.808476388888889</v>
-      </c>
-      <c r="C274" t="n">
         <v>9.82514861111111</v>
       </c>
     </row>
@@ -3376,9 +2551,6 @@
         <v>38991</v>
       </c>
       <c r="B275" t="n">
-        <v>0.76422311827957</v>
-      </c>
-      <c r="C275" t="n">
         <v>9.34477553763441</v>
       </c>
     </row>
@@ -3387,9 +2559,6 @@
         <v>39022</v>
       </c>
       <c r="B276" t="n">
-        <v>0.725592489568846</v>
-      </c>
-      <c r="C276" t="n">
         <v>8.97420723226704</v>
       </c>
     </row>
@@ -3398,9 +2567,6 @@
         <v>39052</v>
       </c>
       <c r="B277" t="n">
-        <v>0.616168010752688</v>
-      </c>
-      <c r="C277" t="n">
         <v>8.08793682795699</v>
       </c>
     </row>
@@ -3409,9 +2575,6 @@
         <v>39083</v>
       </c>
       <c r="B278" t="n">
-        <v>0.647173387096774</v>
-      </c>
-      <c r="C278" t="n">
         <v>8.27531586021505</v>
       </c>
     </row>
@@ -3420,9 +2583,6 @@
         <v>39114</v>
       </c>
       <c r="B279" t="n">
-        <v>0.449727678571429</v>
-      </c>
-      <c r="C279" t="n">
         <v>6.83457738095238</v>
       </c>
     </row>
@@ -3431,9 +2591,6 @@
         <v>39142</v>
       </c>
       <c r="B280" t="n">
-        <v>0.672165322580645</v>
-      </c>
-      <c r="C280" t="n">
         <v>8.54831586021505</v>
       </c>
     </row>
@@ -3442,9 +2599,6 @@
         <v>39173</v>
       </c>
       <c r="B281" t="n">
-        <v>0.540834722222222</v>
-      </c>
-      <c r="C281" t="n">
         <v>7.5119125</v>
       </c>
     </row>
@@ -3453,9 +2607,6 @@
         <v>39203</v>
       </c>
       <c r="B282" t="n">
-        <v>0.641485215053763</v>
-      </c>
-      <c r="C282" t="n">
         <v>8.33647849462366</v>
       </c>
     </row>
@@ -3464,9 +2615,6 @@
         <v>39234</v>
       </c>
       <c r="B283" t="n">
-        <v>0.737713888888889</v>
-      </c>
-      <c r="C283" t="n">
         <v>9.21857916666667</v>
       </c>
     </row>
@@ -3475,9 +2623,6 @@
         <v>39264</v>
       </c>
       <c r="B284" t="n">
-        <v>0.784413978494624</v>
-      </c>
-      <c r="C284" t="n">
         <v>9.60505510752688</v>
       </c>
     </row>
@@ -3486,9 +2631,6 @@
         <v>39295</v>
       </c>
       <c r="B285" t="n">
-        <v>0.884600806451613</v>
-      </c>
-      <c r="C285" t="n">
         <v>10.8655483870968</v>
       </c>
     </row>
@@ -3497,9 +2639,6 @@
         <v>39326</v>
       </c>
       <c r="B286" t="n">
-        <v>0.894298611111111</v>
-      </c>
-      <c r="C286" t="n">
         <v>11.1122152777778</v>
       </c>
     </row>
@@ -3508,9 +2647,6 @@
         <v>39356</v>
       </c>
       <c r="B287" t="n">
-        <v>0.845146702557201</v>
-      </c>
-      <c r="C287" t="n">
         <v>10.2860726783311</v>
       </c>
     </row>
@@ -3519,9 +2655,6 @@
         <v>39387</v>
       </c>
       <c r="B288" t="n">
-        <v>0.748736111111111</v>
-      </c>
-      <c r="C288" t="n">
         <v>9.25820416666667</v>
       </c>
     </row>
@@ -3530,9 +2663,6 @@
         <v>39417</v>
       </c>
       <c r="B289" t="n">
-        <v>0.733099462365591</v>
-      </c>
-      <c r="C289" t="n">
         <v>8.99970833333333</v>
       </c>
     </row>
@@ -3541,9 +2671,6 @@
         <v>39448</v>
       </c>
       <c r="B290" t="n">
-        <v>0.635623655913979</v>
-      </c>
-      <c r="C290" t="n">
         <v>8.24990591397849</v>
       </c>
     </row>
@@ -3552,9 +2679,6 @@
         <v>39479</v>
       </c>
       <c r="B291" t="n">
-        <v>0.554086206896552</v>
-      </c>
-      <c r="C291" t="n">
         <v>7.58729310344828</v>
       </c>
     </row>
@@ -3563,9 +2687,6 @@
         <v>39508</v>
       </c>
       <c r="B292" t="n">
-        <v>0.24644623655914</v>
-      </c>
-      <c r="C292" t="n">
         <v>5.15233064516129</v>
       </c>
     </row>
@@ -3574,9 +2695,6 @@
         <v>39539</v>
       </c>
       <c r="B293" t="n">
-        <v>0.369990277777778</v>
-      </c>
-      <c r="C293" t="n">
         <v>6.08371527777778</v>
       </c>
     </row>
@@ -3585,9 +2703,6 @@
         <v>39569</v>
       </c>
       <c r="B294" t="n">
-        <v>0.485793010752688</v>
-      </c>
-      <c r="C294" t="n">
         <v>7.08786155913979</v>
       </c>
     </row>
@@ -3596,9 +2711,6 @@
         <v>39600</v>
       </c>
       <c r="B295" t="n">
-        <v>0.764726388888889</v>
-      </c>
-      <c r="C295" t="n">
         <v>9.524025</v>
       </c>
     </row>
@@ -3607,9 +2719,6 @@
         <v>39630</v>
       </c>
       <c r="B296" t="n">
-        <v>0.833331989247312</v>
-      </c>
-      <c r="C296" t="n">
         <v>10.2385215053763</v>
       </c>
     </row>
@@ -3618,9 +2727,6 @@
         <v>39661</v>
       </c>
       <c r="B297" t="n">
-        <v>0.794411290322581</v>
-      </c>
-      <c r="C297" t="n">
         <v>9.76715053763441</v>
       </c>
     </row>
@@ -3629,9 +2735,6 @@
         <v>39692</v>
       </c>
       <c r="B298" t="n">
-        <v>0.8459625</v>
-      </c>
-      <c r="C298" t="n">
         <v>10.2221680555556</v>
       </c>
     </row>
@@ -3640,9 +2743,6 @@
         <v>39722</v>
       </c>
       <c r="B299" t="n">
-        <v>0.851740242261104</v>
-      </c>
-      <c r="C299" t="n">
         <v>10.4971561238223</v>
       </c>
     </row>
@@ -3651,9 +2751,6 @@
         <v>39753</v>
       </c>
       <c r="B300" t="n">
-        <v>0.751556944444444</v>
-      </c>
-      <c r="C300" t="n">
         <v>9.12573333333333</v>
       </c>
     </row>
@@ -3662,9 +2759,6 @@
         <v>39783</v>
       </c>
       <c r="B301" t="n">
-        <v>0.634311827956989</v>
-      </c>
-      <c r="C301" t="n">
         <v>8.18281989247312</v>
       </c>
     </row>
@@ -3673,9 +2767,6 @@
         <v>39814</v>
       </c>
       <c r="B302" t="n">
-        <v>0.552399193548387</v>
-      </c>
-      <c r="C302" t="n">
         <v>7.58156451612903</v>
       </c>
     </row>
@@ -3684,9 +2775,6 @@
         <v>39845</v>
       </c>
       <c r="B303" t="n">
-        <v>0.476638392857143</v>
-      </c>
-      <c r="C303" t="n">
         <v>7.03362351190476</v>
       </c>
     </row>
@@ -3695,9 +2783,6 @@
         <v>39873</v>
       </c>
       <c r="B304" t="n">
-        <v>0.382346774193548</v>
-      </c>
-      <c r="C304" t="n">
         <v>6.3489623655914</v>
       </c>
     </row>
@@ -3706,9 +2791,6 @@
         <v>39904</v>
       </c>
       <c r="B305" t="n">
-        <v>0.198738888888889</v>
-      </c>
-      <c r="C305" t="n">
         <v>4.60933888888889</v>
       </c>
     </row>
@@ -3717,9 +2799,6 @@
         <v>39934</v>
       </c>
       <c r="B306" t="n">
-        <v>0.262549731182796</v>
-      </c>
-      <c r="C306" t="n">
         <v>5.21653897849462</v>
       </c>
     </row>
@@ -3728,9 +2807,6 @@
         <v>39965</v>
       </c>
       <c r="B307" t="n">
-        <v>0.610518055555556</v>
-      </c>
-      <c r="C307" t="n">
         <v>8.09392083333333</v>
       </c>
     </row>
@@ -3739,9 +2815,6 @@
         <v>39995</v>
       </c>
       <c r="B308" t="n">
-        <v>0.657149193548387</v>
-      </c>
-      <c r="C308" t="n">
         <v>8.3885685483871</v>
       </c>
     </row>
@@ -3750,9 +2823,6 @@
         <v>40026</v>
       </c>
       <c r="B309" t="n">
-        <v>0.746344086021505</v>
-      </c>
-      <c r="C309" t="n">
         <v>9.21287231182796</v>
       </c>
     </row>
@@ -3761,9 +2831,6 @@
         <v>40057</v>
       </c>
       <c r="B310" t="n">
-        <v>0.760731944444444</v>
-      </c>
-      <c r="C310" t="n">
         <v>9.23480138888889</v>
       </c>
     </row>
@@ -3772,9 +2839,6 @@
         <v>40087</v>
       </c>
       <c r="B311" t="n">
-        <v>0.660154777927322</v>
-      </c>
-      <c r="C311" t="n">
         <v>8.32732974427995</v>
       </c>
     </row>
@@ -3783,9 +2847,6 @@
         <v>40118</v>
       </c>
       <c r="B312" t="n">
-        <v>0.758270833333333</v>
-      </c>
-      <c r="C312" t="n">
         <v>9.2087625</v>
       </c>
     </row>
@@ -3794,9 +2855,6 @@
         <v>40148</v>
       </c>
       <c r="B313" t="n">
-        <v>0.628375</v>
-      </c>
-      <c r="C313" t="n">
         <v>8.14372715053763</v>
       </c>
     </row>
@@ -3805,9 +2863,6 @@
         <v>40179</v>
       </c>
       <c r="B314" t="n">
-        <v>0.493633064516129</v>
-      </c>
-      <c r="C314" t="n">
         <v>7.17382392473118</v>
       </c>
     </row>
@@ -3816,9 +2871,6 @@
         <v>40210</v>
       </c>
       <c r="B315" t="n">
-        <v>0.60553869047619</v>
-      </c>
-      <c r="C315" t="n">
         <v>8.01453571428571</v>
       </c>
     </row>
@@ -3827,9 +2879,6 @@
         <v>40238</v>
       </c>
       <c r="B316" t="n">
-        <v>0.438158602150538</v>
-      </c>
-      <c r="C316" t="n">
         <v>6.82912231182796</v>
       </c>
     </row>
@@ -3838,9 +2887,6 @@
         <v>40269</v>
       </c>
       <c r="B317" t="n">
-        <v>0.572130555555556</v>
-      </c>
-      <c r="C317" t="n">
         <v>7.73789305555556</v>
       </c>
     </row>
@@ -3849,9 +2895,6 @@
         <v>40299</v>
       </c>
       <c r="B318" t="n">
-        <v>0.568236559139785</v>
-      </c>
-      <c r="C318" t="n">
         <v>7.71604838709677</v>
       </c>
     </row>
@@ -3860,9 +2903,6 @@
         <v>40330</v>
       </c>
       <c r="B319" t="n">
-        <v>0.686186111111111</v>
-      </c>
-      <c r="C319" t="n">
         <v>8.765975</v>
       </c>
     </row>
@@ -3871,9 +2911,6 @@
         <v>40360</v>
       </c>
       <c r="B320" t="n">
-        <v>0.811856182795699</v>
-      </c>
-      <c r="C320" t="n">
         <v>10.0568413978495</v>
       </c>
     </row>
@@ -3882,9 +2919,6 @@
         <v>40391</v>
       </c>
       <c r="B321" t="n">
-        <v>0.863862903225806</v>
-      </c>
-      <c r="C321" t="n">
         <v>10.646438172043</v>
       </c>
     </row>
@@ -3893,9 +2927,6 @@
         <v>40422</v>
       </c>
       <c r="B322" t="n">
-        <v>0.8810875</v>
-      </c>
-      <c r="C322" t="n">
         <v>10.8891958333333</v>
       </c>
     </row>
@@ -3904,9 +2935,6 @@
         <v>40452</v>
       </c>
       <c r="B323" t="n">
-        <v>0.662452220726783</v>
-      </c>
-      <c r="C323" t="n">
         <v>8.59206056527591</v>
       </c>
     </row>
@@ -3915,9 +2943,6 @@
         <v>40483</v>
       </c>
       <c r="B324" t="n">
-        <v>0.758622222222222</v>
-      </c>
-      <c r="C324" t="n">
         <v>9.26706111111111</v>
       </c>
     </row>
@@ -3926,9 +2951,6 @@
         <v>40513</v>
       </c>
       <c r="B325" t="n">
-        <v>0.621254032258065</v>
-      </c>
-      <c r="C325" t="n">
         <v>8.18067338709677</v>
       </c>
     </row>
@@ -3937,9 +2959,6 @@
         <v>40544</v>
       </c>
       <c r="B326" t="n">
-        <v>0.478412634408602</v>
-      </c>
-      <c r="C326" t="n">
         <v>7.00466129032258</v>
       </c>
     </row>
@@ -3948,9 +2967,6 @@
         <v>40575</v>
       </c>
       <c r="B327" t="n">
-        <v>0.533931547619048</v>
-      </c>
-      <c r="C327" t="n">
         <v>7.47062797619048</v>
       </c>
     </row>
@@ -3959,9 +2975,6 @@
         <v>40603</v>
       </c>
       <c r="B328" t="n">
-        <v>0.347606182795699</v>
-      </c>
-      <c r="C328" t="n">
         <v>6.05816935483871</v>
       </c>
     </row>
@@ -3970,9 +2983,6 @@
         <v>40634</v>
       </c>
       <c r="B329" t="n">
-        <v>0.415052777777778</v>
-      </c>
-      <c r="C329" t="n">
         <v>6.53888888888889</v>
       </c>
     </row>
@@ -3981,9 +2991,6 @@
         <v>40664</v>
       </c>
       <c r="B330" t="n">
-        <v>0.589934139784946</v>
-      </c>
-      <c r="C330" t="n">
         <v>7.90388709677419</v>
       </c>
     </row>
@@ -3992,9 +2999,6 @@
         <v>40695</v>
       </c>
       <c r="B331" t="n">
-        <v>0.635663888888889</v>
-      </c>
-      <c r="C331" t="n">
         <v>8.30059027777778</v>
       </c>
     </row>
@@ -4003,9 +3007,6 @@
         <v>40725</v>
       </c>
       <c r="B332" t="n">
-        <v>0.718494623655914</v>
-      </c>
-      <c r="C332" t="n">
         <v>9.19433333333333</v>
       </c>
     </row>
@@ -4014,9 +3015,6 @@
         <v>40756</v>
       </c>
       <c r="B333" t="n">
-        <v>0.778133064516129</v>
-      </c>
-      <c r="C333" t="n">
         <v>9.53432661290323</v>
       </c>
     </row>
@@ -4025,9 +3023,6 @@
         <v>40787</v>
       </c>
       <c r="B334" t="n">
-        <v>0.887315277777778</v>
-      </c>
-      <c r="C334" t="n">
         <v>10.9294</v>
       </c>
     </row>
@@ -4036,9 +3031,6 @@
         <v>40817</v>
       </c>
       <c r="B335" t="n">
-        <v>0.727488559892328</v>
-      </c>
-      <c r="C335" t="n">
         <v>9.01356258411844</v>
       </c>
     </row>
@@ -4047,9 +3039,6 @@
         <v>40848</v>
       </c>
       <c r="B336" t="n">
-        <v>0.749436111111111</v>
-      </c>
-      <c r="C336" t="n">
         <v>9.10212083333333</v>
       </c>
     </row>
@@ -4058,9 +3047,6 @@
         <v>40878</v>
       </c>
       <c r="B337" t="n">
-        <v>0.737783602150538</v>
-      </c>
-      <c r="C337" t="n">
         <v>9.00613709677419</v>
       </c>
     </row>
@@ -4069,9 +3055,6 @@
         <v>40909</v>
       </c>
       <c r="B338" t="n">
-        <v>0.694198924731183</v>
-      </c>
-      <c r="C338" t="n">
         <v>8.65102419354839</v>
       </c>
     </row>
@@ -4080,9 +3063,6 @@
         <v>40940</v>
       </c>
       <c r="B339" t="n">
-        <v>0.656204022988506</v>
-      </c>
-      <c r="C339" t="n">
         <v>8.46538218390805</v>
       </c>
     </row>
@@ -4091,9 +3071,6 @@
         <v>40969</v>
       </c>
       <c r="B340" t="n">
-        <v>0.685219086021505</v>
-      </c>
-      <c r="C340" t="n">
         <v>8.58812365591398</v>
       </c>
     </row>
@@ -4102,9 +3079,6 @@
         <v>41000</v>
       </c>
       <c r="B341" t="n">
-        <v>0.679386111111111</v>
-      </c>
-      <c r="C341" t="n">
         <v>8.52828055555556</v>
       </c>
     </row>
@@ -4113,9 +3087,6 @@
         <v>41030</v>
       </c>
       <c r="B342" t="n">
-        <v>0.719525537634409</v>
-      </c>
-      <c r="C342" t="n">
         <v>8.94256317204301</v>
       </c>
     </row>
@@ -4124,9 +3095,6 @@
         <v>41061</v>
       </c>
       <c r="B343" t="n">
-        <v>0.699616666666667</v>
-      </c>
-      <c r="C343" t="n">
         <v>8.78747361111111</v>
       </c>
     </row>
@@ -4135,9 +3103,6 @@
         <v>41091</v>
       </c>
       <c r="B344" t="n">
-        <v>0.804352150537634</v>
-      </c>
-      <c r="C344" t="n">
         <v>9.75740322580645</v>
       </c>
     </row>
@@ -4146,9 +3111,6 @@
         <v>41122</v>
       </c>
       <c r="B345" t="n">
-        <v>0.87408064516129</v>
-      </c>
-      <c r="C345" t="n">
         <v>10.8129260752688</v>
       </c>
     </row>
@@ -4157,9 +3119,6 @@
         <v>41153</v>
       </c>
       <c r="B346" t="n">
-        <v>0.863983333333333</v>
-      </c>
-      <c r="C346" t="n">
         <v>10.4841208333333</v>
       </c>
     </row>
@@ -4168,9 +3127,6 @@
         <v>41183</v>
       </c>
       <c r="B347" t="n">
-        <v>0.854504710632571</v>
-      </c>
-      <c r="C347" t="n">
         <v>10.4448465679677</v>
       </c>
     </row>
@@ -4179,9 +3135,6 @@
         <v>41214</v>
       </c>
       <c r="B348" t="n">
-        <v>0.661551388888889</v>
-      </c>
-      <c r="C348" t="n">
         <v>8.38059166666667</v>
       </c>
     </row>
@@ -4190,9 +3143,6 @@
         <v>41244</v>
       </c>
       <c r="B349" t="n">
-        <v>0.707893817204301</v>
-      </c>
-      <c r="C349" t="n">
         <v>8.71389784946237</v>
       </c>
     </row>
@@ -4201,9 +3151,6 @@
         <v>41275</v>
       </c>
       <c r="B350" t="n">
-        <v>0.653745967741935</v>
-      </c>
-      <c r="C350" t="n">
         <v>8.34036021505376</v>
       </c>
     </row>
@@ -4212,9 +3159,6 @@
         <v>41306</v>
       </c>
       <c r="B351" t="n">
-        <v>0.755946428571429</v>
-      </c>
-      <c r="C351" t="n">
         <v>9.18967113095238</v>
       </c>
     </row>
@@ -4223,9 +3167,6 @@
         <v>41334</v>
       </c>
       <c r="B352" t="n">
-        <v>0.613956989247312</v>
-      </c>
-      <c r="C352" t="n">
         <v>8.10427822580645</v>
       </c>
     </row>
@@ -4234,9 +3175,6 @@
         <v>41365</v>
       </c>
       <c r="B353" t="n">
-        <v>0.490761111111111</v>
-      </c>
-      <c r="C353" t="n">
         <v>7.14938888888889</v>
       </c>
     </row>
@@ -4245,9 +3183,6 @@
         <v>41395</v>
       </c>
       <c r="B354" t="n">
-        <v>0.611650537634409</v>
-      </c>
-      <c r="C354" t="n">
         <v>8.01793817204301</v>
       </c>
     </row>
@@ -4256,9 +3191,6 @@
         <v>41426</v>
       </c>
       <c r="B355" t="n">
-        <v>0.644170833333333</v>
-      </c>
-      <c r="C355" t="n">
         <v>8.28614166666667</v>
       </c>
     </row>
@@ -4267,9 +3199,6 @@
         <v>41456</v>
       </c>
       <c r="B356" t="n">
-        <v>0.678590053763441</v>
-      </c>
-      <c r="C356" t="n">
         <v>8.70362365591398</v>
       </c>
     </row>
@@ -4278,9 +3207,6 @@
         <v>41487</v>
       </c>
       <c r="B357" t="n">
-        <v>0.807399193548387</v>
-      </c>
-      <c r="C357" t="n">
         <v>9.74050806451613</v>
       </c>
     </row>
@@ -4289,9 +3215,6 @@
         <v>41518</v>
       </c>
       <c r="B358" t="n">
-        <v>0.832325</v>
-      </c>
-      <c r="C358" t="n">
         <v>10.0983486111111</v>
       </c>
     </row>
@@ -4300,9 +3223,6 @@
         <v>41548</v>
       </c>
       <c r="B359" t="n">
-        <v>0.795020188425303</v>
-      </c>
-      <c r="C359" t="n">
         <v>9.65575235531628</v>
       </c>
     </row>
@@ -4311,9 +3231,6 @@
         <v>41579</v>
       </c>
       <c r="B360" t="n">
-        <v>0.771533333333333</v>
-      </c>
-      <c r="C360" t="n">
         <v>9.3673</v>
       </c>
     </row>
@@ -4322,9 +3239,6 @@
         <v>41609</v>
       </c>
       <c r="B361" t="n">
-        <v>0.670102150537634</v>
-      </c>
-      <c r="C361" t="n">
         <v>8.43796505376344</v>
       </c>
     </row>
@@ -4333,9 +3247,6 @@
         <v>41640</v>
       </c>
       <c r="B362" t="n">
-        <v>0.707967741935484</v>
-      </c>
-      <c r="C362" t="n">
         <v>8.7557876344086</v>
       </c>
     </row>
@@ -4344,9 +3255,6 @@
         <v>41671</v>
       </c>
       <c r="B363" t="n">
-        <v>0.623883928571429</v>
-      </c>
-      <c r="C363" t="n">
         <v>8.09088690476191</v>
       </c>
     </row>
@@ -4355,9 +3263,6 @@
         <v>41699</v>
       </c>
       <c r="B364" t="n">
-        <v>0.532245967741935</v>
-      </c>
-      <c r="C364" t="n">
         <v>7.43640188172043</v>
       </c>
     </row>
@@ -4366,9 +3271,6 @@
         <v>41730</v>
       </c>
       <c r="B365" t="n">
-        <v>0.486329166666667</v>
-      </c>
-      <c r="C365" t="n">
         <v>7.08955277777778</v>
       </c>
     </row>
@@ -4377,9 +3279,6 @@
         <v>41760</v>
       </c>
       <c r="B366" t="n">
-        <v>0.576225806451613</v>
-      </c>
-      <c r="C366" t="n">
         <v>7.74136827956989</v>
       </c>
     </row>
@@ -4388,9 +3287,6 @@
         <v>41791</v>
       </c>
       <c r="B367" t="n">
-        <v>0.764452777777778</v>
-      </c>
-      <c r="C367" t="n">
         <v>9.33790416666667</v>
       </c>
     </row>
@@ -4399,9 +3295,6 @@
         <v>41821</v>
       </c>
       <c r="B368" t="n">
-        <v>0.773545698924731</v>
-      </c>
-      <c r="C368" t="n">
         <v>9.49486693548387</v>
       </c>
     </row>
@@ -4410,9 +3303,6 @@
         <v>41852</v>
       </c>
       <c r="B369" t="n">
-        <v>0.834576612903226</v>
-      </c>
-      <c r="C369" t="n">
         <v>10.092688172043</v>
       </c>
     </row>
@@ -4421,9 +3311,6 @@
         <v>41883</v>
       </c>
       <c r="B370" t="n">
-        <v>0.781330555555556</v>
-      </c>
-      <c r="C370" t="n">
         <v>9.52234861111111</v>
       </c>
     </row>
@@ -4432,9 +3319,6 @@
         <v>41913</v>
       </c>
       <c r="B371" t="n">
-        <v>0.849192462987887</v>
-      </c>
-      <c r="C371" t="n">
         <v>10.3227025572005</v>
       </c>
     </row>
@@ -4443,9 +3327,6 @@
         <v>41944</v>
       </c>
       <c r="B372" t="n">
-        <v>0.699604166666667</v>
-      </c>
-      <c r="C372" t="n">
         <v>8.69395</v>
       </c>
     </row>
@@ -4454,9 +3335,6 @@
         <v>41974</v>
       </c>
       <c r="B373" t="n">
-        <v>0.711317204301075</v>
-      </c>
-      <c r="C373" t="n">
         <v>8.83413306451613</v>
       </c>
     </row>
@@ -4465,9 +3343,6 @@
         <v>42005</v>
       </c>
       <c r="B374" t="n">
-        <v>0.703338709677419</v>
-      </c>
-      <c r="C374" t="n">
         <v>8.74491935483871</v>
       </c>
     </row>
@@ -4476,9 +3351,6 @@
         <v>42036</v>
       </c>
       <c r="B375" t="n">
-        <v>0.603860119047619</v>
-      </c>
-      <c r="C375" t="n">
         <v>7.97446726190476</v>
       </c>
     </row>
@@ -4487,9 +3359,6 @@
         <v>42064</v>
       </c>
       <c r="B376" t="n">
-        <v>0.508774193548387</v>
-      </c>
-      <c r="C376" t="n">
         <v>7.24886424731183</v>
       </c>
     </row>
@@ -4498,9 +3367,6 @@
         <v>42095</v>
       </c>
       <c r="B377" t="n">
-        <v>0.4574125</v>
-      </c>
-      <c r="C377" t="n">
         <v>6.87430833333333</v>
       </c>
     </row>
@@ -4509,9 +3375,6 @@
         <v>42125</v>
       </c>
       <c r="B378" t="n">
-        <v>0.67641935483871</v>
-      </c>
-      <c r="C378" t="n">
         <v>8.48927822580645</v>
       </c>
     </row>
@@ -4520,9 +3383,6 @@
         <v>42156</v>
       </c>
       <c r="B379" t="n">
-        <v>0.695819444444444</v>
-      </c>
-      <c r="C379" t="n">
         <v>8.70392638888889</v>
       </c>
     </row>
@@ -4531,9 +3391,6 @@
         <v>42186</v>
       </c>
       <c r="B380" t="n">
-        <v>0.791729838709677</v>
-      </c>
-      <c r="C380" t="n">
         <v>9.74194892473118</v>
       </c>
     </row>
@@ -4542,9 +3399,6 @@
         <v>42217</v>
       </c>
       <c r="B381" t="n">
-        <v>0.856896505376344</v>
-      </c>
-      <c r="C381" t="n">
         <v>10.5110551075269</v>
       </c>
     </row>
@@ -4553,9 +3407,6 @@
         <v>42248</v>
       </c>
       <c r="B382" t="n">
-        <v>0.799233333333333</v>
-      </c>
-      <c r="C382" t="n">
         <v>9.63108611111111</v>
       </c>
     </row>
@@ -4564,9 +3415,6 @@
         <v>42278</v>
       </c>
       <c r="B383" t="n">
-        <v>0.808923283983849</v>
-      </c>
-      <c r="C383" t="n">
         <v>9.85067294751009</v>
       </c>
     </row>
@@ -4575,9 +3423,6 @@
         <v>42309</v>
       </c>
       <c r="B384" t="n">
-        <v>0.673777777777778</v>
-      </c>
-      <c r="C384" t="n">
         <v>8.55064861111111</v>
       </c>
     </row>
@@ -4586,9 +3431,6 @@
         <v>42339</v>
       </c>
       <c r="B385" t="n">
-        <v>0.660677419354839</v>
-      </c>
-      <c r="C385" t="n">
         <v>8.39292069892473</v>
       </c>
     </row>
@@ -4597,9 +3439,6 @@
         <v>42370</v>
       </c>
       <c r="B386" t="n">
-        <v>0.413490591397849</v>
-      </c>
-      <c r="C386" t="n">
         <v>6.57397580645161</v>
       </c>
     </row>
@@ -4608,9 +3447,6 @@
         <v>42401</v>
       </c>
       <c r="B387" t="n">
-        <v>0.646830459770115</v>
-      </c>
-      <c r="C387" t="n">
         <v>8.28748706896552</v>
       </c>
     </row>
@@ -4619,9 +3455,6 @@
         <v>42430</v>
       </c>
       <c r="B388" t="n">
-        <v>0.603063172043011</v>
-      </c>
-      <c r="C388" t="n">
         <v>7.92505510752688</v>
       </c>
     </row>
@@ -4630,9 +3463,6 @@
         <v>42461</v>
       </c>
       <c r="B389" t="n">
-        <v>0.695408333333333</v>
-      </c>
-      <c r="C389" t="n">
         <v>8.81561666666667</v>
       </c>
     </row>
@@ -4641,9 +3471,6 @@
         <v>42491</v>
       </c>
       <c r="B390" t="n">
-        <v>0.566123655913979</v>
-      </c>
-      <c r="C390" t="n">
         <v>7.6971061827957</v>
       </c>
     </row>
@@ -4652,9 +3479,6 @@
         <v>42522</v>
       </c>
       <c r="B391" t="n">
-        <v>0.694333333333333</v>
-      </c>
-      <c r="C391" t="n">
         <v>8.84491527777778</v>
       </c>
     </row>
@@ -4663,9 +3487,6 @@
         <v>42552</v>
       </c>
       <c r="B392" t="n">
-        <v>0.827479838709677</v>
-      </c>
-      <c r="C392" t="n">
         <v>10.0906169354839</v>
       </c>
     </row>
@@ -4674,9 +3495,6 @@
         <v>42583</v>
       </c>
       <c r="B393" t="n">
-        <v>0.82726747311828</v>
-      </c>
-      <c r="C393" t="n">
         <v>9.9965497311828</v>
       </c>
     </row>
@@ -4685,9 +3503,6 @@
         <v>42614</v>
       </c>
       <c r="B394" t="n">
-        <v>0.833751388888889</v>
-      </c>
-      <c r="C394" t="n">
         <v>10.1512527777778</v>
       </c>
     </row>
@@ -4696,9 +3511,6 @@
         <v>42644</v>
       </c>
       <c r="B395" t="n">
-        <v>0.829218034993271</v>
-      </c>
-      <c r="C395" t="n">
         <v>10.1790928667564</v>
       </c>
     </row>
@@ -4707,9 +3519,6 @@
         <v>42675</v>
       </c>
       <c r="B396" t="n">
-        <v>0.795243055555556</v>
-      </c>
-      <c r="C396" t="n">
         <v>9.73875416666667</v>
       </c>
     </row>
@@ -4718,9 +3527,6 @@
         <v>42705</v>
       </c>
       <c r="B397" t="n">
-        <v>0.738020161290323</v>
-      </c>
-      <c r="C397" t="n">
         <v>9.05985215053764</v>
       </c>
     </row>
@@ -4729,9 +3535,6 @@
         <v>42736</v>
       </c>
       <c r="B398" t="n">
-        <v>0.694668010752688</v>
-      </c>
-      <c r="C398" t="n">
         <v>8.6537876344086</v>
       </c>
     </row>
@@ -4740,9 +3543,6 @@
         <v>42767</v>
       </c>
       <c r="B399" t="n">
-        <v>0.618816964285714</v>
-      </c>
-      <c r="C399" t="n">
         <v>8.05567113095238</v>
       </c>
     </row>
@@ -4751,9 +3551,6 @@
         <v>42795</v>
       </c>
       <c r="B400" t="n">
-        <v>0.50373252688172</v>
-      </c>
-      <c r="C400" t="n">
         <v>7.22855376344086</v>
       </c>
     </row>
@@ -4762,9 +3559,6 @@
         <v>42826</v>
       </c>
       <c r="B401" t="n">
-        <v>0.564213888888889</v>
-      </c>
-      <c r="C401" t="n">
         <v>7.64149166666667</v>
       </c>
     </row>
@@ -4773,9 +3567,6 @@
         <v>42856</v>
       </c>
       <c r="B402" t="n">
-        <v>0.544708333333333</v>
-      </c>
-      <c r="C402" t="n">
         <v>7.53116666666667</v>
       </c>
     </row>
@@ -4784,9 +3575,6 @@
         <v>42887</v>
       </c>
       <c r="B403" t="n">
-        <v>0.741618055555556</v>
-      </c>
-      <c r="C403" t="n">
         <v>9.21038333333333</v>
       </c>
     </row>
@@ -4795,9 +3583,6 @@
         <v>42917</v>
       </c>
       <c r="B404" t="n">
-        <v>0.79969623655914</v>
-      </c>
-      <c r="C404" t="n">
         <v>10.3015120967742</v>
       </c>
     </row>
@@ -4806,9 +3591,6 @@
         <v>42948</v>
       </c>
       <c r="B405" t="n">
-        <v>0.82811559139785</v>
-      </c>
-      <c r="C405" t="n">
         <v>9.9952688172043</v>
       </c>
     </row>
@@ -4817,9 +3599,6 @@
         <v>42979</v>
       </c>
       <c r="B406" t="n">
-        <v>0.903791666666667</v>
-      </c>
-      <c r="C406" t="n">
         <v>11.1820833333333</v>
       </c>
     </row>
@@ -4828,9 +3607,6 @@
         <v>43009</v>
       </c>
       <c r="B407" t="n">
-        <v>0.846510094212651</v>
-      </c>
-      <c r="C407" t="n">
         <v>10.2679623149394</v>
       </c>
     </row>
@@ -4839,9 +3615,6 @@
         <v>43040</v>
       </c>
       <c r="B408" t="n">
-        <v>0.728526388888889</v>
-      </c>
-      <c r="C408" t="n">
         <v>8.92160138888889</v>
       </c>
     </row>
@@ -4850,9 +3623,6 @@
         <v>43070</v>
       </c>
       <c r="B409" t="n">
-        <v>0.677022849462366</v>
-      </c>
-      <c r="C409" t="n">
         <v>8.49309677419355</v>
       </c>
     </row>
@@ -4861,9 +3631,6 @@
         <v>43101</v>
       </c>
       <c r="B410" t="n">
-        <v>0.584870967741935</v>
-      </c>
-      <c r="C410" t="n">
         <v>7.86778897849462</v>
       </c>
     </row>
@@ -4872,9 +3639,6 @@
         <v>43132</v>
       </c>
       <c r="B411" t="n">
-        <v>0.448306547619048</v>
-      </c>
-      <c r="C411" t="n">
         <v>6.81227529761905</v>
       </c>
     </row>
@@ -4883,9 +3647,6 @@
         <v>43160</v>
       </c>
       <c r="B412" t="n">
-        <v>0.444342741935484</v>
-      </c>
-      <c r="C412" t="n">
         <v>6.81187634408602</v>
       </c>
     </row>
@@ -4894,9 +3655,6 @@
         <v>43191</v>
       </c>
       <c r="B413" t="n">
-        <v>0.440548611111111</v>
-      </c>
-      <c r="C413" t="n">
         <v>6.57256111111111</v>
       </c>
     </row>
@@ -4905,9 +3663,6 @@
         <v>43221</v>
       </c>
       <c r="B414" t="n">
-        <v>0.653439516129032</v>
-      </c>
-      <c r="C414" t="n">
         <v>8.39212365591398</v>
       </c>
     </row>
@@ -4916,9 +3671,6 @@
         <v>43252</v>
       </c>
       <c r="B415" t="n">
-        <v>0.753531944444444</v>
-      </c>
-      <c r="C415" t="n">
         <v>9.23291388888889</v>
       </c>
     </row>
@@ -4927,9 +3679,6 @@
         <v>43282</v>
       </c>
       <c r="B416" t="n">
-        <v>0.807073924731183</v>
-      </c>
-      <c r="C416" t="n">
         <v>9.79470295698925</v>
       </c>
     </row>
@@ -4938,9 +3687,6 @@
         <v>43313</v>
       </c>
       <c r="B417" t="n">
-        <v>0.808670698924731</v>
-      </c>
-      <c r="C417" t="n">
         <v>9.84418682795699</v>
       </c>
     </row>
@@ -4949,9 +3695,6 @@
         <v>43344</v>
       </c>
       <c r="B418" t="n">
-        <v>0.848356944444444</v>
-      </c>
-      <c r="C418" t="n">
         <v>10.2658152777778</v>
       </c>
     </row>
@@ -4960,9 +3703,6 @@
         <v>43374</v>
       </c>
       <c r="B419" t="n">
-        <v>0.732299731182796</v>
-      </c>
-      <c r="C419" t="n">
         <v>9.08411155913979</v>
       </c>
     </row>
@@ -4971,9 +3711,6 @@
         <v>43405</v>
       </c>
       <c r="B420" t="n">
-        <v>0.798833101529903</v>
-      </c>
-      <c r="C420" t="n">
         <v>9.6299388038943</v>
       </c>
     </row>
@@ -4982,9 +3719,6 @@
         <v>43435</v>
       </c>
       <c r="B421" t="n">
-        <v>0.638399193548387</v>
-      </c>
-      <c r="C421" t="n">
         <v>8.27388978494624</v>
       </c>
     </row>
@@ -4993,9 +3727,6 @@
         <v>43466</v>
       </c>
       <c r="B422" t="n">
-        <v>0.62797311827957</v>
-      </c>
-      <c r="C422" t="n">
         <v>8.17836290322581</v>
       </c>
     </row>
@@ -5004,9 +3735,6 @@
         <v>43497</v>
       </c>
       <c r="B423" t="n">
-        <v>0.401837797619048</v>
-      </c>
-      <c r="C423" t="n">
         <v>6.47650446428571</v>
       </c>
     </row>
@@ -5015,9 +3743,6 @@
         <v>43525</v>
       </c>
       <c r="B424" t="n">
-        <v>0.34622311827957</v>
-      </c>
-      <c r="C424" t="n">
         <v>6.03084677419355</v>
       </c>
     </row>
@@ -5026,9 +3751,6 @@
         <v>43556</v>
       </c>
       <c r="B425" t="n">
-        <v>0.379419444444444</v>
-      </c>
-      <c r="C425" t="n">
         <v>6.27521388888889</v>
       </c>
     </row>
@@ -5037,9 +3759,6 @@
         <v>43586</v>
       </c>
       <c r="B426" t="n">
-        <v>0.61042876344086</v>
-      </c>
-      <c r="C426" t="n">
         <v>8.0221935483871</v>
       </c>
     </row>
@@ -5048,9 +3767,6 @@
         <v>43617</v>
       </c>
       <c r="B427" t="n">
-        <v>0.739493055555556</v>
-      </c>
-      <c r="C427" t="n">
         <v>9.12244027777778</v>
       </c>
     </row>
@@ -5059,9 +3775,6 @@
         <v>43647</v>
       </c>
       <c r="B428" t="n">
-        <v>0.711537634408602</v>
-      </c>
-      <c r="C428" t="n">
         <v>8.86241935483871</v>
       </c>
     </row>
@@ -5070,9 +3783,6 @@
         <v>43678</v>
       </c>
       <c r="B429" t="n">
-        <v>0.851412634408602</v>
-      </c>
-      <c r="C429" t="n">
         <v>10.2794233870968</v>
       </c>
     </row>
@@ -5081,9 +3791,6 @@
         <v>43709</v>
       </c>
       <c r="B430" t="n">
-        <v>0.831211111111111</v>
-      </c>
-      <c r="C430" t="n">
         <v>10.0270916666667</v>
       </c>
     </row>
@@ -5092,9 +3799,6 @@
         <v>43739</v>
       </c>
       <c r="B431" t="n">
-        <v>0.787516129032258</v>
-      </c>
-      <c r="C431" t="n">
         <v>9.68672043010753</v>
       </c>
     </row>
@@ -5103,9 +3807,6 @@
         <v>43770</v>
       </c>
       <c r="B432" t="n">
-        <v>0.718670833333333</v>
-      </c>
-      <c r="C432" t="n">
         <v>8.89346527777778</v>
       </c>
     </row>
@@ -5114,9 +3815,6 @@
         <v>43800</v>
       </c>
       <c r="B433" t="n">
-        <v>0.664233870967742</v>
-      </c>
-      <c r="C433" t="n">
         <v>8.5234811827957</v>
       </c>
     </row>
@@ -5125,9 +3823,6 @@
         <v>43831</v>
       </c>
       <c r="B434" t="n">
-        <v>0.460224462365591</v>
-      </c>
-      <c r="C434" t="n">
         <v>6.9311747311828</v>
       </c>
     </row>
@@ -5136,9 +3831,6 @@
         <v>43862</v>
       </c>
       <c r="B435" t="n">
-        <v>0.454382183908046</v>
-      </c>
-      <c r="C435" t="n">
         <v>6.8665617816092</v>
       </c>
     </row>
@@ -5147,9 +3839,6 @@
         <v>43891</v>
       </c>
       <c r="B436" t="n">
-        <v>0.267350806451613</v>
-      </c>
-      <c r="C436" t="n">
         <v>5.44751344086021</v>
       </c>
     </row>
@@ -5158,9 +3847,6 @@
         <v>43922</v>
       </c>
       <c r="B437" t="n">
-        <v>0.402766666666667</v>
-      </c>
-      <c r="C437" t="n">
         <v>6.427975</v>
       </c>
     </row>
@@ -5169,9 +3855,6 @@
         <v>43952</v>
       </c>
       <c r="B438" t="n">
-        <v>0.554340053763441</v>
-      </c>
-      <c r="C438" t="n">
         <v>7.59318682795699</v>
       </c>
     </row>
@@ -5180,9 +3863,6 @@
         <v>43983</v>
       </c>
       <c r="B439" t="n">
-        <v>0.678548611111111</v>
-      </c>
-      <c r="C439" t="n">
         <v>8.74716111111111</v>
       </c>
     </row>
@@ -5191,9 +3871,6 @@
         <v>44013</v>
       </c>
       <c r="B440" t="n">
-        <v>0.74584811827957</v>
-      </c>
-      <c r="C440" t="n">
         <v>9.18727553763441</v>
       </c>
     </row>
@@ -5202,9 +3879,6 @@
         <v>44044</v>
       </c>
       <c r="B441" t="n">
-        <v>0.845637096774194</v>
-      </c>
-      <c r="C441" t="n">
         <v>10.2656357526882</v>
       </c>
     </row>
@@ -5213,9 +3887,6 @@
         <v>44075</v>
       </c>
       <c r="B442" t="n">
-        <v>0.819226388888889</v>
-      </c>
-      <c r="C442" t="n">
         <v>9.8424</v>
       </c>
     </row>
@@ -5224,9 +3895,6 @@
         <v>44105</v>
       </c>
       <c r="B443" t="n">
-        <v>0.689577956989247</v>
-      </c>
-      <c r="C443" t="n">
         <v>8.68040322580645</v>
       </c>
     </row>
@@ -5235,9 +3903,6 @@
         <v>44136</v>
       </c>
       <c r="B444" t="n">
-        <v>0.693148611111111</v>
-      </c>
-      <c r="C444" t="n">
         <v>8.74209861111111</v>
       </c>
     </row>
@@ -5246,9 +3911,6 @@
         <v>44166</v>
       </c>
       <c r="B445" t="n">
-        <v>0.728148048452221</v>
-      </c>
-      <c r="C445" t="n">
         <v>8.93627725437416</v>
       </c>
     </row>
@@ -5257,9 +3919,6 @@
         <v>44197</v>
       </c>
       <c r="B446" t="n">
-        <v>0.622561827956989</v>
-      </c>
-      <c r="C446" t="n">
         <v>8.05434274193548</v>
       </c>
     </row>
@@ -5268,9 +3927,6 @@
         <v>44228</v>
       </c>
       <c r="B447" t="n">
-        <v>0.503154761904762</v>
-      </c>
-      <c r="C447" t="n">
         <v>7.24643154761905</v>
       </c>
     </row>
@@ -5279,9 +3935,6 @@
         <v>44256</v>
       </c>
       <c r="B448" t="n">
-        <v>0.503698924731183</v>
-      </c>
-      <c r="C448" t="n">
         <v>7.21024596774194</v>
       </c>
     </row>
@@ -5290,9 +3943,6 @@
         <v>44287</v>
       </c>
       <c r="B449" t="n">
-        <v>0.521234722222222</v>
-      </c>
-      <c r="C449" t="n">
         <v>7.39879861111111</v>
       </c>
     </row>
@@ -5301,9 +3951,6 @@
         <v>44317</v>
       </c>
       <c r="B450" t="n">
-        <v>0.584736559139785</v>
-      </c>
-      <c r="C450" t="n">
         <v>7.85488172043011</v>
       </c>
     </row>
@@ -5312,9 +3959,6 @@
         <v>44348</v>
       </c>
       <c r="B451" t="n">
-        <v>0.642345833333333</v>
-      </c>
-      <c r="C451" t="n">
         <v>8.28226944444445</v>
       </c>
     </row>
@@ -5323,9 +3967,6 @@
         <v>44378</v>
       </c>
       <c r="B452" t="n">
-        <v>0.729942204301075</v>
-      </c>
-      <c r="C452" t="n">
         <v>9.03980107526882</v>
       </c>
     </row>
@@ -5334,9 +3975,6 @@
         <v>44409</v>
       </c>
       <c r="B453" t="n">
-        <v>0.860798387096774</v>
-      </c>
-      <c r="C453" t="n">
         <v>10.4779690860215</v>
       </c>
     </row>
@@ -5345,9 +3983,6 @@
         <v>44440</v>
       </c>
       <c r="B454" t="n">
-        <v>0.789130555555556</v>
-      </c>
-      <c r="C454" t="n">
         <v>9.58676666666667</v>
       </c>
     </row>
@@ -5356,9 +3991,6 @@
         <v>44470</v>
       </c>
       <c r="B455" t="n">
-        <v>0.712157258064516</v>
-      </c>
-      <c r="C455" t="n">
         <v>8.85341666666667</v>
       </c>
     </row>
@@ -5367,9 +3999,6 @@
         <v>44501</v>
       </c>
       <c r="B456" t="n">
-        <v>0.636897222222222</v>
-      </c>
-      <c r="C456" t="n">
         <v>8.22654166666667</v>
       </c>
     </row>
@@ -5378,9 +4007,6 @@
         <v>44531</v>
       </c>
       <c r="B457" t="n">
-        <v>0.634458333333333</v>
-      </c>
-      <c r="C457" t="n">
         <v>8.23528897849462</v>
       </c>
     </row>
@@ -5389,9 +4015,6 @@
         <v>44562</v>
       </c>
       <c r="B458" t="n">
-        <v>0.457790322580645</v>
-      </c>
-      <c r="C458" t="n">
         <v>6.87839516129032</v>
       </c>
     </row>
@@ -5400,9 +4023,6 @@
         <v>44593</v>
       </c>
       <c r="B459" t="n">
-        <v>0.541510416666667</v>
-      </c>
-      <c r="C459" t="n">
         <v>7.49517410714286</v>
       </c>
     </row>
@@ -5411,9 +4031,6 @@
         <v>44621</v>
       </c>
       <c r="B460" t="n">
-        <v>0.417603494623656</v>
-      </c>
-      <c r="C460" t="n">
         <v>6.56570161290323</v>
       </c>
     </row>
@@ -5422,9 +4039,6 @@
         <v>44652</v>
       </c>
       <c r="B461" t="n">
-        <v>0.471018055555556</v>
-      </c>
-      <c r="C461" t="n">
         <v>6.95046805555556</v>
       </c>
     </row>
@@ -5433,9 +4047,6 @@
         <v>44682</v>
       </c>
       <c r="B462" t="n">
-        <v>0.568172043010753</v>
-      </c>
-      <c r="C462" t="n">
         <v>7.68970967741935</v>
       </c>
     </row>
@@ -5444,9 +4055,6 @@
         <v>44713</v>
       </c>
       <c r="B463" t="n">
-        <v>0.544433333333333</v>
-      </c>
-      <c r="C463" t="n">
         <v>7.574125</v>
       </c>
     </row>
@@ -5455,9 +4063,6 @@
         <v>44743</v>
       </c>
       <c r="B464" t="n">
-        <v>0.775311827956989</v>
-      </c>
-      <c r="C464" t="n">
         <v>9.54774193548387</v>
       </c>
     </row>
@@ -5466,9 +4071,6 @@
         <v>44774</v>
       </c>
       <c r="B465" t="n">
-        <v>0.790954301075269</v>
-      </c>
-      <c r="C465" t="n">
         <v>9.70292204301075</v>
       </c>
     </row>
@@ -5477,9 +4079,6 @@
         <v>44805</v>
       </c>
       <c r="B466" t="n">
-        <v>0.765918055555556</v>
-      </c>
-      <c r="C466" t="n">
         <v>9.30155833333333</v>
       </c>
     </row>
@@ -5488,9 +4087,6 @@
         <v>44835</v>
       </c>
       <c r="B467" t="n">
-        <v>0.770461021505376</v>
-      </c>
-      <c r="C467" t="n">
         <v>9.3773938172043</v>
       </c>
     </row>
@@ -5499,9 +4095,6 @@
         <v>44866</v>
       </c>
       <c r="B468" t="n">
-        <v>0.533166666666667</v>
-      </c>
-      <c r="C468" t="n">
         <v>7.42875833333333</v>
       </c>
     </row>
@@ -5510,9 +4103,6 @@
         <v>44896</v>
       </c>
       <c r="B469" t="n">
-        <v>0.59294623655914</v>
-      </c>
-      <c r="C469" t="n">
         <v>7.90421774193548</v>
       </c>
     </row>
@@ -5521,9 +4111,6 @@
         <v>44927</v>
       </c>
       <c r="B470" t="n">
-        <v>0.576474462365591</v>
-      </c>
-      <c r="C470" t="n">
         <v>7.72899731182796</v>
       </c>
     </row>
@@ -5532,9 +4119,6 @@
         <v>44958</v>
       </c>
       <c r="B471" t="n">
-        <v>0.592607142857143</v>
-      </c>
-      <c r="C471" t="n">
         <v>7.85484821428571</v>
       </c>
     </row>
@@ -5543,9 +4127,6 @@
         <v>44986</v>
       </c>
       <c r="B472" t="n">
-        <v>0.450858870967742</v>
-      </c>
-      <c r="C472" t="n">
         <v>6.72669489247312</v>
       </c>
     </row>
@@ -5554,9 +4135,6 @@
         <v>45017</v>
       </c>
       <c r="B473" t="n">
-        <v>0.387738888888889</v>
-      </c>
-      <c r="C473" t="n">
         <v>6.36993194444444</v>
       </c>
     </row>
@@ -5565,9 +4143,6 @@
         <v>45047</v>
       </c>
       <c r="B474" t="n">
-        <v>0.552697580645161</v>
-      </c>
-      <c r="C474" t="n">
         <v>7.63783333333333</v>
       </c>
     </row>
@@ -5576,9 +4151,6 @@
         <v>45078</v>
       </c>
       <c r="B475" t="n">
-        <v>0.705275</v>
-      </c>
-      <c r="C475" t="n">
         <v>8.87393888888889</v>
       </c>
     </row>
@@ -5587,9 +4159,6 @@
         <v>45108</v>
       </c>
       <c r="B476" t="n">
-        <v>0.728643817204301</v>
-      </c>
-      <c r="C476" t="n">
         <v>9.17161559139785</v>
       </c>
     </row>
@@ -5598,9 +4167,6 @@
         <v>45139</v>
       </c>
       <c r="B477" t="n">
-        <v>0.711157258064516</v>
-      </c>
-      <c r="C477" t="n">
         <v>8.91270430107527</v>
       </c>
     </row>
@@ -5609,9 +4175,6 @@
         <v>45170</v>
       </c>
       <c r="B478" t="n">
-        <v>0.785483333333333</v>
-      </c>
-      <c r="C478" t="n">
         <v>9.6352</v>
       </c>
     </row>
@@ -5620,9 +4183,6 @@
         <v>45200</v>
       </c>
       <c r="B479" t="n">
-        <v>0.734715053763441</v>
-      </c>
-      <c r="C479" t="n">
         <v>9.04542338709677</v>
       </c>
     </row>
@@ -5631,9 +4191,6 @@
         <v>45231</v>
       </c>
       <c r="B480" t="n">
-        <v>0.643123611111111</v>
-      </c>
-      <c r="C480" t="n">
         <v>8.29330416666667</v>
       </c>
     </row>
@@ -5642,9 +4199,6 @@
         <v>45261</v>
       </c>
       <c r="B481" t="n">
-        <v>0.592478494623656</v>
-      </c>
-      <c r="C481" t="n">
         <v>7.89271639784946</v>
       </c>
     </row>
